--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -10083,7 +10083,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京丰台区西四环双林东路服务中心</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>北京市大兴区大兴龙湖天街一层中庭</t>
+          <t>双林东路8号万开基地二期B座</t>
         </is>
       </c>
     </row>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区西四环双林东路服务中心</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>双林东路8号万开基地二期B座</t>
+          <t>北京市大兴区大兴龙湖天街一层中庭</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>小米汽车安徽省合肥市庐阳区万象汇</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>东塘路80号合肥巢湖万达广场1F</t>
+          <t>安徽省合肥市庐阳区庐阳万象汇1F1号门入口</t>
         </is>
       </c>
     </row>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市庐阳区万象汇</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>安徽省合肥市庐阳区庐阳万象汇1F1号门入口</t>
+          <t>东塘路80号合肥巢湖万达广场1F</t>
         </is>
       </c>
     </row>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>理想汽车潍坊青州汽车园零售展厅</t>
+          <t>理想汽车潍坊寿光授权钣喷中心（广宝店）</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>青州市玲珑山北路2359号</t>
+          <t>山东省潍坊市寿光市文家街道圣城西街666号</t>
         </is>
       </c>
     </row>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>理想汽车潍坊寿光授权钣喷中心（广宝店）</t>
+          <t>理想汽车潍坊青州汽车园零售展厅</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>山东省潍坊市寿光市文家街道圣城西街666号</t>
+          <t>青州市玲珑山北路2359号</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•成都惠王陵西路</t>
+          <t>鸿蒙智行智界用户中心•成都武侯大道</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市龙泉驿区惠王陵西路155号</t>
+          <t>四川省成都市武侯区武侯大道顺江段61号</t>
         </is>
       </c>
     </row>
@@ -11055,7 +11055,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•成都武侯大道</t>
+          <t>鸿蒙智行尚界用户中心•成都惠王陵西路</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市武侯区武侯大道顺江段61号</t>
+          <t>四川省成都市龙泉驿区惠王陵西路155号</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•宁波下应</t>
+          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
+          <t>AITO授权用户中心•宁波下应</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江服务中心（振兴东路店）</t>
+          <t>理想汽车衢州吾悦广场零售中心</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>衢州市衢江区振兴东路599号</t>
+          <t>浙江省衢州市柯城区白云中大道路99号吾悦广场1019-1商铺理想汽车</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>理想汽车衢州吾悦广场零售中心</t>
+          <t>理想汽车衢州衢江服务中心（振兴东路店）</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区白云中大道路99号吾悦广场1019-1商铺理想汽车</t>
+          <t>衢州市衢江区振兴东路599号</t>
         </is>
       </c>
     </row>
@@ -12075,7 +12075,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-福田电气化体验馆</t>
+          <t>深圳中升悦晟-罗湖卫星展厅</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
+          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
         </is>
       </c>
     </row>
@@ -12102,7 +12102,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-罗湖卫星展厅</t>
+          <t>深圳中升悦晟-福田电气化体验馆</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
+          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
         </is>
       </c>
     </row>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（长楹龙湖）</t>
+          <t>鸿蒙智行授权用户中心•北京王四营</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
+          <t>北京市朝阳区王四营339号</t>
         </is>
       </c>
     </row>
@@ -12210,7 +12210,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京王四营</t>
+          <t>华为智能生活馆•北京颐堤港</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营339号</t>
+          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
         </is>
       </c>
     </row>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京颐堤港</t>
+          <t>华为授权体验店（长楹龙湖）</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
+          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（星河COCOCity）</t>
+          <t>华为授权体验店（南湖天地）</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
+          <t>浙江省嘉兴市南湖区南湖街道171号</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（南湖天地）</t>
+          <t>华为授权体验店（西田城）</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区南湖街道171号</t>
+          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
         </is>
       </c>
     </row>
@@ -12804,7 +12804,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（西田城）</t>
+          <t>华为授权体验店（星河COCOCity）</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
+          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
         </is>
       </c>
     </row>
@@ -13128,17 +13128,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13148,29 +13148,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13180,29 +13180,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13212,29 +13212,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13244,29 +13244,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省珠海市香洲区前山工业区华威路103号A-23号 → 广东省珠海市香洲区前山工业区华威路103号二手车车库103-A-23号</t>
+          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13276,29 +13276,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13308,29 +13308,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13340,29 +13340,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13372,29 +13372,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
+          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13404,29 +13404,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13436,29 +13436,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
+          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13468,29 +13468,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
+          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13500,29 +13500,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13532,29 +13532,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13564,29 +13564,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13596,29 +13596,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
         </is>
       </c>
     </row>
@@ -13640,17 +13640,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
         </is>
       </c>
     </row>
@@ -13672,17 +13672,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13692,29 +13692,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13724,29 +13724,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13756,29 +13756,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
+          <t>广东省珠海市香洲区前山工业区华威路103号A-23号 → 广东省珠海市香洲区前山工业区华威路103号二手车车库103-A-23号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13788,29 +13788,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
+          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13820,29 +13820,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
+          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13852,7 +13852,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
+          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
         </is>
       </c>
     </row>
@@ -13864,17 +13864,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13884,29 +13884,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13916,29 +13916,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
         </is>
       </c>
     </row>
@@ -13960,17 +13960,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13980,29 +13980,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14012,29 +14012,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
+          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14044,7 +14044,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
@@ -14056,17 +14056,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14076,29 +14076,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14108,29 +14108,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14140,7 +14140,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
@@ -14152,17 +14152,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
@@ -14216,17 +14216,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14243,22 +14243,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14280,17 +14280,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14312,17 +14312,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14344,17 +14344,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14376,17 +14376,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14408,17 +14408,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14472,17 +14472,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14504,17 +14504,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14536,17 +14536,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14568,17 +14568,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14600,17 +14600,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14632,17 +14632,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14664,17 +14664,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14696,17 +14696,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14728,17 +14728,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14760,17 +14760,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14787,22 +14787,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14819,22 +14819,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14851,22 +14851,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14888,17 +14888,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14920,17 +14920,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14952,17 +14952,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14984,17 +14984,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15016,17 +15016,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15048,17 +15048,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15080,17 +15080,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15112,17 +15112,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15144,17 +15144,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15176,17 +15176,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15208,17 +15208,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15235,7 +15235,7 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -15245,12 +15245,12 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15272,17 +15272,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15304,17 +15304,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15336,17 +15336,17 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15368,17 +15368,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15400,17 +15400,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15432,17 +15432,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -15464,17 +15464,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15501,12 +15501,12 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15528,17 +15528,17 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15560,17 +15560,17 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15592,17 +15592,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15619,22 +15619,22 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15656,17 +15656,17 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -15693,12 +15693,12 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15720,17 +15720,17 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15752,17 +15752,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15784,17 +15784,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15816,17 +15816,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15848,17 +15848,17 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15880,17 +15880,17 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15907,22 +15907,22 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15944,17 +15944,17 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15971,22 +15971,22 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16008,17 +16008,17 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16035,22 +16035,22 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16067,22 +16067,22 @@
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -16104,17 +16104,17 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16136,17 +16136,17 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16168,17 +16168,17 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16200,17 +16200,17 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -16232,17 +16232,17 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16264,17 +16264,17 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16296,17 +16296,17 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16333,12 +16333,12 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16360,17 +16360,17 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16392,17 +16392,17 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16424,17 +16424,17 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -16456,17 +16456,17 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16488,17 +16488,17 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16520,17 +16520,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16552,17 +16552,17 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16579,22 +16579,22 @@
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16611,22 +16611,22 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16648,17 +16648,17 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -16680,17 +16680,17 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16712,17 +16712,17 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16739,22 +16739,22 @@
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中信恒业</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中源恒业</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -16776,17 +16776,17 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16803,22 +16803,22 @@
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16840,17 +16840,17 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -16872,17 +16872,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16904,17 +16904,17 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16931,22 +16931,22 @@
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>牡丹江中信恒业</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>牡丹江中源恒业</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16963,22 +16963,22 @@
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -16995,22 +16995,22 @@
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17032,17 +17032,17 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -17064,17 +17064,17 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17096,17 +17096,17 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道服务中心</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17128,17 +17128,17 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17160,17 +17160,17 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17192,17 +17192,17 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17224,17 +17224,17 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17256,17 +17256,17 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17283,22 +17283,22 @@
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17325,12 +17325,12 @@
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17352,17 +17352,17 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17384,17 +17384,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17416,17 +17416,17 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17443,22 +17443,22 @@
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17480,17 +17480,17 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17507,22 +17507,22 @@
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17539,22 +17539,22 @@
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -17576,17 +17576,17 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17608,17 +17608,17 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17640,17 +17640,17 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17672,17 +17672,17 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17704,17 +17704,17 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17731,22 +17731,22 @@
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17768,17 +17768,17 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17800,17 +17800,17 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17832,17 +17832,17 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17864,17 +17864,17 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17896,17 +17896,17 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17928,17 +17928,17 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17955,22 +17955,22 @@
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -17987,22 +17987,22 @@
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18024,17 +18024,17 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18056,17 +18056,17 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18088,17 +18088,17 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18120,17 +18120,17 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -18152,17 +18152,17 @@
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18179,22 +18179,22 @@
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -18216,17 +18216,17 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18248,17 +18248,17 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -18280,17 +18280,17 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -18312,17 +18312,17 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -18344,17 +18344,17 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -18376,17 +18376,17 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -18403,22 +18403,22 @@
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -18440,17 +18440,17 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -18472,17 +18472,17 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -18504,17 +18504,17 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -18536,17 +18536,17 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -18568,17 +18568,17 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
@@ -18659,22 +18659,22 @@
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•威海青岛南路</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
@@ -18684,29 +18684,29 @@
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 69%</t>
+          <t>地址相似度 88%</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
+          <t>鸿蒙智行尚界用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
+          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 88%</t>
+          <t>地址相似度 69%</t>
         </is>
       </c>
     </row>
@@ -18728,17 +18728,17 @@
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路授权服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
@@ -18748,29 +18748,29 @@
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
+          <t>潍坊易豪4S中心</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
+          <t>潍坊鑫易豪4S中心</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
@@ -18780,7 +18780,7 @@
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
@@ -18792,17 +18792,17 @@
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
+          <t>小米汽车天津西青区卫津南路授权服务中心</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
+          <t>小米汽车天津西青区卫津南路服务中心</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
@@ -18824,17 +18824,17 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18856,17 +18856,17 @@
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
@@ -18876,7 +18876,7 @@
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18888,17 +18888,17 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
@@ -18908,7 +18908,7 @@
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18920,17 +18920,17 @@
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
@@ -18940,7 +18940,7 @@
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18979,22 +18979,22 @@
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>潍坊易豪4S中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>潍坊鑫易豪4S中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -19016,17 +19016,17 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
+          <t>小米汽车兴义市桔康路授权服务中心</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
+          <t>小米汽车兴义市桔康路服务中心</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
@@ -19036,7 +19036,7 @@
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 91%</t>
         </is>
       </c>
     </row>
@@ -19048,17 +19048,17 @@
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路授权服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 91%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -10083,7 +10083,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京丰台区西四环双林东路服务中心</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>北京市大兴区大兴龙湖天街一层中庭</t>
+          <t>双林东路8号万开基地二期B座</t>
         </is>
       </c>
     </row>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区西四环双林东路服务中心</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>双林东路8号万开基地二期B座</t>
+          <t>北京市大兴区大兴龙湖天街一层中庭</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>小米汽车安徽省合肥市庐阳区万象汇</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>东塘路80号合肥巢湖万达广场1F</t>
+          <t>安徽省合肥市庐阳区庐阳万象汇1F1号门入口</t>
         </is>
       </c>
     </row>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市庐阳区万象汇</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>安徽省合肥市庐阳区庐阳万象汇1F1号门入口</t>
+          <t>东塘路80号合肥巢湖万达广场1F</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市江津区爱情海购物广场</t>
+          <t>小米汽车重庆市永川区永川万达</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>重庆市江津区爱情海购物广场L1层中庭</t>
+          <t>中国重庆市永川区星光大道789号永川万达</t>
         </is>
       </c>
     </row>
@@ -10353,7 +10353,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区永川万达</t>
+          <t>小米汽车重庆市江津区爱情海购物广场</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>中国重庆市永川区星光大道789号永川万达</t>
+          <t>重庆市江津区爱情海购物广场L1层中庭</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春中东新天地零售中心</t>
+          <t>理想汽车长春华润万象城零售中心</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区亚泰大街1138号</t>
+          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
         </is>
       </c>
     </row>
@@ -10569,7 +10569,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春华润万象城零售中心</t>
+          <t>理想汽车长春中东新天地零售中心</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
+          <t>吉林省长春市南关区亚泰大街1138号</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•成都武侯大道</t>
+          <t>鸿蒙智行尚界用户中心•成都惠王陵西路</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市武侯区武侯大道顺江段61号</t>
+          <t>四川省成都市龙泉驿区惠王陵西路155号</t>
         </is>
       </c>
     </row>
@@ -11055,7 +11055,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•成都惠王陵西路</t>
+          <t>鸿蒙智行智界用户中心•成都武侯大道</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市龙泉驿区惠王陵西路155号</t>
+          <t>四川省成都市武侯区武侯大道顺江段61号</t>
         </is>
       </c>
     </row>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京颐堤港</t>
+          <t>华为授权体验店（长楹龙湖）</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
+          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
         </is>
       </c>
     </row>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（长楹龙湖）</t>
+          <t>华为智能生活馆•北京颐堤港</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
+          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
         </is>
       </c>
     </row>
@@ -12480,7 +12480,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛凯德Mall</t>
+          <t>华为智能生活馆•青岛乐客城</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
+          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛乐客城</t>
+          <t>华为智能生活馆•青岛凯德Mall</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
+          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（南湖天地）</t>
+          <t>华为授权体验店（星河COCOCity）</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区南湖街道171号</t>
+          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
         </is>
       </c>
     </row>
@@ -12804,7 +12804,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（星河COCOCity）</t>
+          <t>华为授权体验店（南湖天地）</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
+          <t>浙江省嘉兴市南湖区南湖街道171号</t>
         </is>
       </c>
     </row>
@@ -13123,22 +13123,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13148,29 +13148,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
+          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
@@ -13192,17 +13192,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13212,7 +13212,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
         </is>
       </c>
     </row>
@@ -13224,17 +13224,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13244,29 +13244,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13276,29 +13276,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13308,29 +13308,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13340,7 +13340,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
         </is>
       </c>
     </row>
@@ -13352,17 +13352,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13372,29 +13372,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13404,29 +13404,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13436,29 +13436,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
+          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
+          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
         </is>
       </c>
     </row>
@@ -13507,22 +13507,22 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13532,29 +13532,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13564,29 +13564,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13596,29 +13596,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13628,29 +13628,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13660,29 +13660,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
+          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13692,29 +13692,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13724,29 +13724,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13756,29 +13756,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
+          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13788,7 +13788,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
+          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
         </is>
       </c>
     </row>
@@ -13800,17 +13800,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13820,14 +13820,14 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -13837,12 +13837,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13852,29 +13852,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
@@ -13896,17 +13896,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13916,29 +13916,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
+          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13948,29 +13948,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
@@ -13992,17 +13992,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14012,29 +14012,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14044,29 +14044,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14076,29 +14076,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14108,29 +14108,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14140,7 +14140,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
@@ -14152,17 +14152,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
+          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
         </is>
       </c>
     </row>
@@ -14216,17 +14216,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14248,17 +14248,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14280,17 +14280,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14312,17 +14312,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14339,22 +14339,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>牡丹江中信恒业</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>牡丹江中源恒业</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14371,22 +14371,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14408,17 +14408,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14440,17 +14440,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14472,17 +14472,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14509,12 +14509,12 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14536,17 +14536,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14568,17 +14568,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14600,17 +14600,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14632,17 +14632,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14659,7 +14659,7 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -14669,12 +14669,12 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14696,17 +14696,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14728,17 +14728,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14760,17 +14760,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14792,17 +14792,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14824,17 +14824,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14856,17 +14856,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14888,17 +14888,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14920,17 +14920,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14952,17 +14952,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14984,17 +14984,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15016,17 +15016,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15048,17 +15048,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15080,17 +15080,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15112,17 +15112,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15144,17 +15144,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15176,17 +15176,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15208,17 +15208,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15240,17 +15240,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15272,17 +15272,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15304,17 +15304,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15331,7 +15331,7 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15368,17 +15368,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15400,17 +15400,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15432,17 +15432,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -15464,17 +15464,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15496,17 +15496,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15528,17 +15528,17 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15560,17 +15560,17 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15592,17 +15592,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15624,17 +15624,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15656,17 +15656,17 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -15688,17 +15688,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15720,17 +15720,17 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15747,22 +15747,22 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15784,17 +15784,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15816,17 +15816,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15843,22 +15843,22 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15880,17 +15880,17 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15912,17 +15912,17 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15944,17 +15944,17 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15976,17 +15976,17 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16008,17 +16008,17 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16040,17 +16040,17 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16072,17 +16072,17 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -16104,17 +16104,17 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16136,17 +16136,17 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16168,17 +16168,17 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16200,17 +16200,17 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -16232,17 +16232,17 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16264,17 +16264,17 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16296,17 +16296,17 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16323,22 +16323,22 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16355,22 +16355,22 @@
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16397,12 +16397,12 @@
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16419,22 +16419,22 @@
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -16456,17 +16456,17 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16488,17 +16488,17 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16520,17 +16520,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16552,17 +16552,17 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16579,22 +16579,22 @@
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16616,17 +16616,17 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16648,17 +16648,17 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -16675,22 +16675,22 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中信恒业</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中源恒业</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16712,17 +16712,17 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16744,17 +16744,17 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -16776,17 +16776,17 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16808,17 +16808,17 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16840,17 +16840,17 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -16872,17 +16872,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16904,17 +16904,17 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16936,17 +16936,17 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16963,22 +16963,22 @@
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -16995,22 +16995,22 @@
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17032,17 +17032,17 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -17059,22 +17059,22 @@
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17091,22 +17091,22 @@
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17128,17 +17128,17 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17160,17 +17160,17 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17192,17 +17192,17 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17219,22 +17219,22 @@
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17256,17 +17256,17 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17288,17 +17288,17 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17320,17 +17320,17 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17352,17 +17352,17 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17384,17 +17384,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17416,17 +17416,17 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17448,17 +17448,17 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17480,17 +17480,17 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17512,17 +17512,17 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17544,17 +17544,17 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -17571,22 +17571,22 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17613,12 +17613,12 @@
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17640,17 +17640,17 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17672,17 +17672,17 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17704,17 +17704,17 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17736,17 +17736,17 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17768,17 +17768,17 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17800,17 +17800,17 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道服务中心</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17832,17 +17832,17 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17864,17 +17864,17 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17891,22 +17891,22 @@
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17928,17 +17928,17 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17960,17 +17960,17 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -17992,17 +17992,17 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18024,17 +18024,17 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18056,17 +18056,17 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18088,17 +18088,17 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18120,17 +18120,17 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -18152,17 +18152,17 @@
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18184,17 +18184,17 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -18211,22 +18211,22 @@
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18248,17 +18248,17 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -18275,22 +18275,22 @@
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
+          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -18312,17 +18312,17 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -18339,22 +18339,22 @@
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -18376,17 +18376,17 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -18403,22 +18403,22 @@
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -18440,17 +18440,17 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -18472,17 +18472,17 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -18504,17 +18504,17 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -18536,17 +18536,17 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -18568,17 +18568,17 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
@@ -18728,17 +18728,17 @@
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
@@ -18748,7 +18748,7 @@
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18760,17 +18760,17 @@
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
@@ -18792,17 +18792,17 @@
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
@@ -18812,29 +18812,29 @@
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
+          <t>潍坊易豪4S中心</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
+          <t>潍坊鑫易豪4S中心</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
@@ -18856,17 +18856,17 @@
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
@@ -18876,7 +18876,7 @@
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18888,17 +18888,17 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路授权服务中心</t>
+          <t>小米汽车天津西青区卫津南路授权服务中心</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路服务中心</t>
+          <t>小米汽车天津西青区卫津南路服务中心</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
@@ -18908,7 +18908,7 @@
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 91%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18920,17 +18920,17 @@
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
+          <t>小米汽车兴义市桔康路授权服务中心</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
+          <t>小米汽车兴义市桔康路服务中心</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
@@ -18940,7 +18940,7 @@
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 91%</t>
         </is>
       </c>
     </row>
@@ -18952,17 +18952,17 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路授权服务中心</t>
+          <t>小米汽车江西萍乡安源区萍乡天虹</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路服务中心</t>
+          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
@@ -18972,7 +18972,7 @@
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18984,17 +18984,17 @@
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
@@ -19011,22 +19011,22 @@
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>潍坊易豪4S中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>潍坊鑫易豪4S中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
@@ -19036,7 +19036,7 @@
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -19053,12 +19053,12 @@
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西萍乡安源区萍乡天虹</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -10137,7 +10137,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市庐阳区万象汇</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>安徽省合肥市庐阳区庐阳万象汇1F1号门入口</t>
+          <t>东塘路80号合肥巢湖万达广场1F</t>
         </is>
       </c>
     </row>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>小米汽车安徽省合肥市庐阳区万象汇</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>东塘路80号合肥巢湖万达广场1F</t>
+          <t>安徽省合肥市庐阳区庐阳万象汇1F1号门入口</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区永川万达</t>
+          <t>小米汽车重庆市江津区爱情海购物广场</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>中国重庆市永川区星光大道789号永川万达</t>
+          <t>重庆市江津区爱情海购物广场L1层中庭</t>
         </is>
       </c>
     </row>
@@ -10353,7 +10353,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市江津区爱情海购物广场</t>
+          <t>小米汽车重庆市永川区永川万达</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>重庆市江津区爱情海购物广场L1层中庭</t>
+          <t>中国重庆市永川区星光大道789号永川万达</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京龙湖长楹天街</t>
+          <t>鸿蒙智行智界用户中心•北京房山城关</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通路1号院龙湖长楹天街东区一层B栋-2F-C32，B栋-1F-19a，B栋-2F-21，B栋-1F-19b，B栋-2F-19a，B栋-2F-19b，B栋-2F-20号商铺</t>
+          <t>北京市房山区城关街道顾八路一区2号</t>
         </is>
       </c>
     </row>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•北京房山城关</t>
+          <t>华为智能生活馆•北京龙湖长楹天街</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>北京市房山区城关街道顾八路一区2号</t>
+          <t>北京市朝阳区常通路1号院龙湖长楹天街东区一层B栋-2F-C32，B栋-1F-19a，B栋-2F-21，B栋-1F-19b，B栋-2F-19a，B栋-2F-19b，B栋-2F-20号商铺</t>
         </is>
       </c>
     </row>
@@ -12075,7 +12075,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-福田电气化体验馆</t>
+          <t>深圳中升悦晟-罗湖卫星展厅</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
+          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
         </is>
       </c>
     </row>
@@ -12102,7 +12102,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-罗湖卫星展厅</t>
+          <t>深圳中升悦晟-福田电气化体验馆</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
+          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（西田城）</t>
+          <t>华为授权体验店（星河COCOCity）</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
+          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（星河COCOCity）</t>
+          <t>华为授权体验店（西田城）</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
+          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
         </is>
       </c>
     </row>
@@ -13123,22 +13123,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13148,29 +13148,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13180,29 +13180,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13212,29 +13212,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
+          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13244,29 +13244,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13276,29 +13276,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
+          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
         </is>
       </c>
     </row>
@@ -13320,17 +13320,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13340,29 +13340,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13372,7 +13372,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
@@ -13384,17 +13384,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
@@ -13416,17 +13416,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13436,29 +13436,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
@@ -13480,17 +13480,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13500,7 +13500,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>广东省珠海市香洲区前山工业区华威路103号A-23号 → 广东省珠海市香洲区前山工业区华威路103号二手车车库103-A-23号</t>
+          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
         </is>
       </c>
     </row>
@@ -13512,17 +13512,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13532,14 +13532,14 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -13549,12 +13549,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13564,29 +13564,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13596,29 +13596,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
+          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13628,29 +13628,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13660,29 +13660,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13692,29 +13692,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13724,29 +13724,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
+          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13756,29 +13756,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
+          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13788,29 +13788,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13820,7 +13820,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
@@ -13832,17 +13832,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13852,14 +13852,14 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -13869,12 +13869,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
         </is>
       </c>
     </row>
@@ -13896,17 +13896,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13916,29 +13916,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13948,29 +13948,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13980,29 +13980,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14012,29 +14012,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14044,29 +14044,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
+          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
         </is>
       </c>
     </row>
@@ -14088,17 +14088,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14108,29 +14108,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>广东省珠海市香洲区前山工业区华威路103号A-23号 → 广东省珠海市香洲区前山工业区华威路103号二手车车库103-A-23号</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14140,29 +14140,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
+          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
         </is>
       </c>
     </row>
@@ -14216,17 +14216,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14248,17 +14248,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14280,17 +14280,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14312,17 +14312,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14339,22 +14339,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中信恒业</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中源恒业</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14376,17 +14376,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14408,17 +14408,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14440,17 +14440,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14472,17 +14472,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14504,17 +14504,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14536,17 +14536,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14568,17 +14568,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14605,12 +14605,12 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14632,17 +14632,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14659,22 +14659,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14696,17 +14696,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14728,17 +14728,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14760,17 +14760,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14792,17 +14792,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14824,17 +14824,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14883,22 +14883,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14920,17 +14920,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14952,17 +14952,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14984,17 +14984,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15021,12 +15021,12 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15048,17 +15048,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15080,17 +15080,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15112,17 +15112,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15144,17 +15144,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15176,17 +15176,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15208,17 +15208,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15240,17 +15240,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道服务中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15272,17 +15272,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15304,17 +15304,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15336,17 +15336,17 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15368,17 +15368,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15400,17 +15400,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15427,22 +15427,22 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -15464,17 +15464,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15501,12 +15501,12 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15528,17 +15528,17 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15560,17 +15560,17 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15587,22 +15587,22 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15624,17 +15624,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15656,17 +15656,17 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -15693,12 +15693,12 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15720,17 +15720,17 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15747,22 +15747,22 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15784,17 +15784,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15821,12 +15821,12 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15843,22 +15843,22 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15885,12 +15885,12 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15912,17 +15912,17 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15939,22 +15939,22 @@
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15976,17 +15976,17 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16008,17 +16008,17 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16035,22 +16035,22 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16099,22 +16099,22 @@
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16136,17 +16136,17 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16168,17 +16168,17 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16200,17 +16200,17 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -16232,17 +16232,17 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16264,17 +16264,17 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16296,17 +16296,17 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16328,17 +16328,17 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16355,22 +16355,22 @@
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16387,22 +16387,22 @@
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16424,17 +16424,17 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -16461,12 +16461,12 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16483,7 +16483,7 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
@@ -16493,12 +16493,12 @@
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16520,17 +16520,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16552,17 +16552,17 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16584,17 +16584,17 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16616,17 +16616,17 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16648,17 +16648,17 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -16685,12 +16685,12 @@
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16712,17 +16712,17 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16739,22 +16739,22 @@
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>牡丹江中信恒业</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>牡丹江中源恒业</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -16776,17 +16776,17 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16813,12 +16813,12 @@
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16835,7 +16835,7 @@
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
@@ -16845,12 +16845,12 @@
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -16872,17 +16872,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16904,17 +16904,17 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16936,17 +16936,17 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16963,22 +16963,22 @@
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -16995,22 +16995,22 @@
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17027,22 +17027,22 @@
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -17064,17 +17064,17 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17096,17 +17096,17 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17128,17 +17128,17 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17160,17 +17160,17 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17192,17 +17192,17 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17219,22 +17219,22 @@
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17256,17 +17256,17 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17288,17 +17288,17 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17315,22 +17315,22 @@
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17352,17 +17352,17 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17384,17 +17384,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17416,17 +17416,17 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17448,17 +17448,17 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17480,17 +17480,17 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17512,17 +17512,17 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17544,17 +17544,17 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -17576,17 +17576,17 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17608,17 +17608,17 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17640,17 +17640,17 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17672,17 +17672,17 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17704,17 +17704,17 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17736,17 +17736,17 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17768,17 +17768,17 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17800,17 +17800,17 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17832,17 +17832,17 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17859,22 +17859,22 @@
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17891,22 +17891,22 @@
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17928,17 +17928,17 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17960,17 +17960,17 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -17987,22 +17987,22 @@
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18024,17 +18024,17 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18056,17 +18056,17 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18088,17 +18088,17 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18120,17 +18120,17 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -18152,17 +18152,17 @@
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18184,17 +18184,17 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -18216,17 +18216,17 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18248,17 +18248,17 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -18275,22 +18275,22 @@
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -18312,17 +18312,17 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -18339,22 +18339,22 @@
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -18376,17 +18376,17 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -18408,17 +18408,17 @@
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -18440,17 +18440,17 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -18472,17 +18472,17 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -18504,17 +18504,17 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -18536,17 +18536,17 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -18568,17 +18568,17 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
@@ -18595,22 +18595,22 @@
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
+          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
+          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
@@ -18620,29 +18620,29 @@
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 60%</t>
+          <t>地址相似度 88%</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
+          <t>鸿蒙智行尚界用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
+          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
@@ -18652,29 +18652,29 @@
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 88%</t>
+          <t>地址相似度 69%</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
+          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
+          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
@@ -18684,29 +18684,29 @@
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 88%</t>
+          <t>地址相似度 60%</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•威海青岛南路</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 69%</t>
+          <t>地址相似度 88%</t>
         </is>
       </c>
     </row>
@@ -18728,17 +18728,17 @@
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
@@ -18748,7 +18748,7 @@
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18760,17 +18760,17 @@
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
@@ -18780,29 +18780,29 @@
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
+          <t>潍坊易豪4S中心</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
+          <t>潍坊鑫易豪4S中心</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
@@ -18812,29 +18812,29 @@
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>潍坊易豪4S中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>潍坊鑫易豪4S中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18856,17 +18856,17 @@
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
+          <t>小米汽车江西萍乡安源区萍乡天虹</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
+          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
@@ -18876,7 +18876,7 @@
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18888,17 +18888,17 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路授权服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
@@ -18908,7 +18908,7 @@
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18920,17 +18920,17 @@
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路授权服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
@@ -18940,7 +18940,7 @@
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 91%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18952,17 +18952,17 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西萍乡安源区萍乡天虹</t>
+          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
+          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
@@ -18984,17 +18984,17 @@
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -19016,17 +19016,17 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
+          <t>小米汽车天津西青区卫津南路授权服务中心</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
+          <t>小米汽车天津西青区卫津南路服务中心</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
@@ -19036,7 +19036,7 @@
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -19048,17 +19048,17 @@
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>小米汽车兴义市桔康路授权服务中心</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>小米汽车兴义市桔康路服务中心</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 91%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -10137,7 +10137,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>小米汽车安徽省合肥市庐阳区万象汇</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>东塘路80号合肥巢湖万达广场1F</t>
+          <t>安徽省合肥市庐阳区庐阳万象汇1F1号门入口</t>
         </is>
       </c>
     </row>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市庐阳区万象汇</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>安徽省合肥市庐阳区庐阳万象汇1F1号门入口</t>
+          <t>东塘路80号合肥巢湖万达广场1F</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市江津区爱情海购物广场</t>
+          <t>小米汽车重庆市永川区永川万达</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>重庆市江津区爱情海购物广场L1层中庭</t>
+          <t>中国重庆市永川区星光大道789号永川万达</t>
         </is>
       </c>
     </row>
@@ -10353,7 +10353,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区永川万达</t>
+          <t>小米汽车重庆市江津区爱情海购物广场</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>中国重庆市永川区星光大道789号永川万达</t>
+          <t>重庆市江津区爱情海购物广场L1层中庭</t>
         </is>
       </c>
     </row>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>理想汽车潍坊寿光授权钣喷中心（广宝店）</t>
+          <t>理想汽车潍坊青州汽车园零售展厅</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>山东省潍坊市寿光市文家街道圣城西街666号</t>
+          <t>青州市玲珑山北路2359号</t>
         </is>
       </c>
     </row>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>理想汽车潍坊青州汽车园零售展厅</t>
+          <t>理想汽车潍坊寿光授权钣喷中心（广宝店）</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>青州市玲珑山北路2359号</t>
+          <t>山东省潍坊市寿光市文家街道圣城西街666号</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•北京房山城关</t>
+          <t>华为智能生活馆•北京龙湖长楹天街</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>北京市房山区城关街道顾八路一区2号</t>
+          <t>北京市朝阳区常通路1号院龙湖长楹天街东区一层B栋-2F-C32，B栋-1F-19a，B栋-2F-21，B栋-1F-19b，B栋-2F-19a，B栋-2F-19b，B栋-2F-20号商铺</t>
         </is>
       </c>
     </row>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京龙湖长楹天街</t>
+          <t>鸿蒙智行智界用户中心•北京房山城关</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通路1号院龙湖长楹天街东区一层B栋-2F-C32，B栋-1F-19a，B栋-2F-21，B栋-1F-19b，B栋-2F-19a，B栋-2F-19b，B栋-2F-20号商铺</t>
+          <t>北京市房山区城关街道顾八路一区2号</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•成都惠王陵西路</t>
+          <t>鸿蒙智行智界用户中心•成都武侯大道</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市龙泉驿区惠王陵西路155号</t>
+          <t>四川省成都市武侯区武侯大道顺江段61号</t>
         </is>
       </c>
     </row>
@@ -11055,7 +11055,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•成都武侯大道</t>
+          <t>鸿蒙智行尚界用户中心•成都惠王陵西路</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市武侯区武侯大道顺江段61号</t>
+          <t>四川省成都市龙泉驿区惠王陵西路155号</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•宁波下应</t>
+          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
+          <t>AITO授权用户中心•宁波下应</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>理想汽车衢州吾悦广场零售中心</t>
+          <t>理想汽车衢州衢江服务中心（振兴东路店）</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区白云中大道路99号吾悦广场1019-1商铺理想汽车</t>
+          <t>衢州市衢江区振兴东路599号</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江服务中心（振兴东路店）</t>
+          <t>理想汽车衢州吾悦广场零售中心</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>衢州市衢江区振兴东路599号</t>
+          <t>浙江省衢州市柯城区白云中大道路99号吾悦广场1019-1商铺理想汽车</t>
         </is>
       </c>
     </row>
@@ -12075,7 +12075,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-罗湖卫星展厅</t>
+          <t>深圳中升悦晟-福田电气化体验馆</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
+          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
         </is>
       </c>
     </row>
@@ -12102,7 +12102,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-福田电气化体验馆</t>
+          <t>深圳中升悦晟-罗湖卫星展厅</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
+          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
         </is>
       </c>
     </row>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（长楹龙湖）</t>
+          <t>鸿蒙智行授权用户中心•北京王四营</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
+          <t>北京市朝阳区王四营339号</t>
         </is>
       </c>
     </row>
@@ -12210,7 +12210,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京王四营</t>
+          <t>华为智能生活馆•北京颐堤港</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营339号</t>
+          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
         </is>
       </c>
     </row>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京颐堤港</t>
+          <t>华为授权体验店（长楹龙湖）</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
+          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
         </is>
       </c>
     </row>
@@ -12480,7 +12480,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛乐客城</t>
+          <t>华为智能生活馆•青岛凯德Mall</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
+          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛凯德Mall</t>
+          <t>华为智能生活馆•青岛乐客城</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
+          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -13128,17 +13128,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13148,29 +13148,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13180,29 +13180,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13212,29 +13212,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
+          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13244,29 +13244,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13276,29 +13276,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
@@ -13320,17 +13320,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13340,29 +13340,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13372,7 +13372,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
@@ -13384,17 +13384,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>广东省珠海市香洲区前山工业区华威路103号A-23号 → 广东省珠海市香洲区前山工业区华威路103号二手车车库103-A-23号</t>
         </is>
       </c>
     </row>
@@ -13416,17 +13416,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13436,29 +13436,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
         </is>
       </c>
     </row>
@@ -13480,17 +13480,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13500,7 +13500,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
@@ -13517,12 +13517,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13532,29 +13532,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13564,29 +13564,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13596,7 +13596,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
+          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
         </is>
       </c>
     </row>
@@ -13608,17 +13608,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13628,29 +13628,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13660,29 +13660,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13692,7 +13692,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
+          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
         </is>
       </c>
     </row>
@@ -13704,17 +13704,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13724,29 +13724,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13756,29 +13756,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13788,29 +13788,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13820,29 +13820,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13852,29 +13852,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13884,29 +13884,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
+          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13916,29 +13916,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13948,29 +13948,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
+          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13980,29 +13980,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14012,29 +14012,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14044,29 +14044,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
+          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14076,29 +14076,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
+          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14108,29 +14108,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>广东省珠海市香洲区前山工业区华威路103号A-23号 → 广东省珠海市香洲区前山工业区华威路103号二手车车库103-A-23号</t>
+          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14140,29 +14140,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
+          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
         </is>
       </c>
     </row>
@@ -14221,12 +14221,12 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14253,12 +14253,12 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14280,17 +14280,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14312,17 +14312,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14339,22 +14339,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14376,17 +14376,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14408,17 +14408,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14440,17 +14440,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14472,17 +14472,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14504,17 +14504,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14536,17 +14536,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14568,17 +14568,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14600,17 +14600,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14627,22 +14627,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14659,22 +14659,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14696,17 +14696,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14733,12 +14733,12 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14760,17 +14760,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14792,17 +14792,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14824,17 +14824,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14856,17 +14856,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14883,22 +14883,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14915,22 +14915,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14952,17 +14952,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14984,17 +14984,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15016,17 +15016,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15048,17 +15048,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15080,17 +15080,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15112,17 +15112,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15139,22 +15139,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15176,17 +15176,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15208,17 +15208,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15240,17 +15240,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15272,17 +15272,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15304,17 +15304,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15336,17 +15336,17 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15368,17 +15368,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15400,17 +15400,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15427,22 +15427,22 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -15464,17 +15464,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15496,17 +15496,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15523,22 +15523,22 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15560,17 +15560,17 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15587,22 +15587,22 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15624,17 +15624,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15656,17 +15656,17 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -15688,17 +15688,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15720,17 +15720,17 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15752,17 +15752,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15779,22 +15779,22 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15811,22 +15811,22 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15848,17 +15848,17 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15880,17 +15880,17 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15912,17 +15912,17 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15939,22 +15939,22 @@
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15976,17 +15976,17 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16003,22 +16003,22 @@
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16045,12 +16045,12 @@
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16072,17 +16072,17 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -16099,22 +16099,22 @@
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16136,17 +16136,17 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16168,17 +16168,17 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16200,17 +16200,17 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -16232,17 +16232,17 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16264,17 +16264,17 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16296,17 +16296,17 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16328,17 +16328,17 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16360,17 +16360,17 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16392,17 +16392,17 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16424,17 +16424,17 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -16456,17 +16456,17 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16488,17 +16488,17 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16520,17 +16520,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16552,17 +16552,17 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16584,17 +16584,17 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16616,17 +16616,17 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16648,17 +16648,17 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -16685,12 +16685,12 @@
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16712,17 +16712,17 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16739,22 +16739,22 @@
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中信恒业</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中源恒业</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -16776,17 +16776,17 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16808,17 +16808,17 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16835,22 +16835,22 @@
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -16872,17 +16872,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16909,12 +16909,12 @@
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16936,17 +16936,17 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16963,22 +16963,22 @@
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -17000,17 +17000,17 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17027,22 +17027,22 @@
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -17064,17 +17064,17 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17096,17 +17096,17 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17128,17 +17128,17 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17155,22 +17155,22 @@
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
+          <t>牡丹江中信恒业</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
+          <t>牡丹江中源恒业</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17192,17 +17192,17 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17224,17 +17224,17 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17261,12 +17261,12 @@
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17288,17 +17288,17 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17315,22 +17315,22 @@
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17352,17 +17352,17 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17384,17 +17384,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17416,17 +17416,17 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17448,17 +17448,17 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17480,17 +17480,17 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17512,17 +17512,17 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17544,17 +17544,17 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -17576,17 +17576,17 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道服务中心</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17608,17 +17608,17 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17640,17 +17640,17 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17672,17 +17672,17 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17704,17 +17704,17 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17736,17 +17736,17 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17768,17 +17768,17 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17800,17 +17800,17 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17832,17 +17832,17 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17859,22 +17859,22 @@
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17896,17 +17896,17 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17928,17 +17928,17 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17960,17 +17960,17 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -17987,22 +17987,22 @@
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18024,17 +18024,17 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18056,17 +18056,17 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18088,17 +18088,17 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18120,17 +18120,17 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -18147,22 +18147,22 @@
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18184,17 +18184,17 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -18216,17 +18216,17 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18248,17 +18248,17 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -18280,17 +18280,17 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -18312,17 +18312,17 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -18344,17 +18344,17 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -18376,17 +18376,17 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -18408,17 +18408,17 @@
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -18440,17 +18440,17 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -18467,22 +18467,22 @@
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -18536,17 +18536,17 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -18568,17 +18568,17 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
@@ -18595,22 +18595,22 @@
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
+          <t>鸿蒙智行尚界用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
+          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
@@ -18620,29 +18620,29 @@
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 88%</t>
+          <t>地址相似度 69%</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•威海青岛南路</t>
+          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
+          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
@@ -18652,29 +18652,29 @@
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 69%</t>
+          <t>地址相似度 60%</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
+          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
+          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
@@ -18684,7 +18684,7 @@
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 60%</t>
+          <t>地址相似度 88%</t>
         </is>
       </c>
     </row>
@@ -18728,17 +18728,17 @@
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
@@ -18748,7 +18748,7 @@
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18760,17 +18760,17 @@
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
@@ -18780,29 +18780,29 @@
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>潍坊易豪4S中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>潍坊鑫易豪4S中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
@@ -18812,7 +18812,7 @@
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18824,17 +18824,17 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
@@ -18856,17 +18856,17 @@
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西萍乡安源区萍乡天虹</t>
+          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
+          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
@@ -18888,17 +18888,17 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
+          <t>小米汽车江西萍乡安源区萍乡天虹</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
+          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
@@ -18908,29 +18908,29 @@
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>潍坊易豪4S中心</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>潍坊鑫易豪4S中心</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
@@ -18940,7 +18940,7 @@
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
@@ -18952,17 +18952,17 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
@@ -18972,7 +18972,7 @@
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -10542,7 +10542,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春华润万象城零售中心</t>
+          <t>理想汽车长春中东新天地零售中心</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
+          <t>吉林省长春市南关区亚泰大街1138号</t>
         </is>
       </c>
     </row>
@@ -10569,7 +10569,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春中东新天地零售中心</t>
+          <t>理想汽车长春华润万象城零售中心</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区亚泰大街1138号</t>
+          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
         </is>
       </c>
     </row>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>理想汽车潍坊青州汽车园零售展厅</t>
+          <t>理想汽车潍坊寿光授权钣喷中心（广宝店）</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>青州市玲珑山北路2359号</t>
+          <t>山东省潍坊市寿光市文家街道圣城西街666号</t>
         </is>
       </c>
     </row>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>理想汽车潍坊寿光授权钣喷中心（广宝店）</t>
+          <t>理想汽车潍坊青州汽车园零售展厅</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>山东省潍坊市寿光市文家街道圣城西街666号</t>
+          <t>青州市玲珑山北路2359号</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京龙湖长楹天街</t>
+          <t>鸿蒙智行智界用户中心•北京房山城关</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通路1号院龙湖长楹天街东区一层B栋-2F-C32，B栋-1F-19a，B栋-2F-21，B栋-1F-19b，B栋-2F-19a，B栋-2F-19b，B栋-2F-20号商铺</t>
+          <t>北京市房山区城关街道顾八路一区2号</t>
         </is>
       </c>
     </row>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•北京房山城关</t>
+          <t>华为智能生活馆•北京龙湖长楹天街</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>北京市房山区城关街道顾八路一区2号</t>
+          <t>北京市朝阳区常通路1号院龙湖长楹天街东区一层B栋-2F-C32，B栋-1F-19a，B栋-2F-21，B栋-1F-19b，B栋-2F-19a，B栋-2F-19b，B栋-2F-20号商铺</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•成都武侯大道</t>
+          <t>鸿蒙智行尚界用户中心•成都惠王陵西路</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市武侯区武侯大道顺江段61号</t>
+          <t>四川省成都市龙泉驿区惠王陵西路155号</t>
         </is>
       </c>
     </row>
@@ -11055,7 +11055,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•成都惠王陵西路</t>
+          <t>鸿蒙智行智界用户中心•成都武侯大道</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市龙泉驿区惠王陵西路155号</t>
+          <t>四川省成都市武侯区武侯大道顺江段61号</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
+          <t>AITO授权用户中心•宁波下应</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•宁波下应</t>
+          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -12075,7 +12075,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-福田电气化体验馆</t>
+          <t>深圳中升悦晟-罗湖卫星展厅</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
+          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
         </is>
       </c>
     </row>
@@ -12102,7 +12102,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-罗湖卫星展厅</t>
+          <t>深圳中升悦晟-福田电气化体验馆</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
+          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
         </is>
       </c>
     </row>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京王四营</t>
+          <t>华为授权体验店（长楹龙湖）</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营339号</t>
+          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
         </is>
       </c>
     </row>
@@ -12210,7 +12210,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京颐堤港</t>
+          <t>鸿蒙智行授权用户中心•北京王四营</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
+          <t>北京市朝阳区王四营339号</t>
         </is>
       </c>
     </row>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（长楹龙湖）</t>
+          <t>华为智能生活馆•北京颐堤港</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
+          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
         </is>
       </c>
     </row>
@@ -12480,7 +12480,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛凯德Mall</t>
+          <t>华为智能生活馆•青岛乐客城</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
+          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛乐客城</t>
+          <t>华为智能生活馆•青岛凯德Mall</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
+          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（星河COCOCity）</t>
+          <t>华为授权体验店（西田城）</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
+          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（西田城）</t>
+          <t>华为授权体验店（星河COCOCity）</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
+          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
         </is>
       </c>
     </row>
@@ -13128,17 +13128,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13148,29 +13148,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
+          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
@@ -13192,17 +13192,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13212,7 +13212,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
@@ -13224,17 +13224,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13244,29 +13244,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13276,29 +13276,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13308,29 +13308,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13340,29 +13340,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13372,29 +13372,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13404,29 +13404,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省珠海市香洲区前山工业区华威路103号A-23号 → 广东省珠海市香洲区前山工业区华威路103号二手车车库103-A-23号</t>
+          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
+          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
         </is>
       </c>
     </row>
@@ -13448,17 +13448,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13468,29 +13468,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13500,7 +13500,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
@@ -13512,17 +13512,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13532,29 +13532,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13564,29 +13564,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13596,7 +13596,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
@@ -13608,17 +13608,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13628,29 +13628,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>广东省珠海市香洲区前山工业区华威路103号A-23号 → 广东省珠海市香洲区前山工业区华威路103号二手车车库103-A-23号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13660,29 +13660,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13692,7 +13692,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
@@ -13704,17 +13704,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13724,29 +13724,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
+          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13756,29 +13756,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13788,7 +13788,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
@@ -13800,17 +13800,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13820,29 +13820,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13852,29 +13852,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13884,29 +13884,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13916,29 +13916,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
+          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
+          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
         </is>
       </c>
     </row>
@@ -13960,17 +13960,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13980,29 +13980,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14012,29 +14012,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14044,29 +14044,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
+          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14076,29 +14076,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14108,7 +14108,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
@@ -14147,22 +14147,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
+          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
         </is>
       </c>
     </row>
@@ -14216,17 +14216,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14248,17 +14248,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14280,17 +14280,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14312,17 +14312,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14349,12 +14349,12 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14376,17 +14376,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14408,17 +14408,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14440,17 +14440,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14472,17 +14472,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14504,17 +14504,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14541,12 +14541,12 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14568,17 +14568,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14600,17 +14600,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14627,22 +14627,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14659,22 +14659,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14696,17 +14696,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14728,17 +14728,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14760,17 +14760,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14792,17 +14792,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14829,12 +14829,12 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14856,17 +14856,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14893,12 +14893,12 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14915,22 +14915,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14952,17 +14952,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14984,17 +14984,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15016,17 +15016,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15048,17 +15048,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15080,17 +15080,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15112,17 +15112,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15139,22 +15139,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15171,22 +15171,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>牡丹江中信恒业</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>牡丹江中源恒业</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15208,17 +15208,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15240,17 +15240,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15272,17 +15272,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15304,17 +15304,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15331,22 +15331,22 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15368,17 +15368,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15395,22 +15395,22 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15432,17 +15432,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -15464,17 +15464,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15496,17 +15496,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15523,22 +15523,22 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15555,22 +15555,22 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15592,17 +15592,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15624,17 +15624,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15656,17 +15656,17 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -15688,17 +15688,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15720,17 +15720,17 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15752,17 +15752,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15779,22 +15779,22 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15811,22 +15811,22 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15848,17 +15848,17 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15880,17 +15880,17 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15907,22 +15907,22 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15949,12 +15949,12 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15976,17 +15976,17 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16003,22 +16003,22 @@
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16035,22 +16035,22 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16072,17 +16072,17 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -16104,17 +16104,17 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16136,17 +16136,17 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16168,17 +16168,17 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16200,17 +16200,17 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -16232,17 +16232,17 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16264,17 +16264,17 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16296,17 +16296,17 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16328,17 +16328,17 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16360,17 +16360,17 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16397,12 +16397,12 @@
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16424,17 +16424,17 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -16456,17 +16456,17 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16493,12 +16493,12 @@
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16520,17 +16520,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16547,22 +16547,22 @@
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16584,17 +16584,17 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16616,17 +16616,17 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16648,17 +16648,17 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -16680,17 +16680,17 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16707,22 +16707,22 @@
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16744,17 +16744,17 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -16776,17 +16776,17 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16808,17 +16808,17 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16840,17 +16840,17 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -16872,17 +16872,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16904,17 +16904,17 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16936,17 +16936,17 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16963,22 +16963,22 @@
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -17000,17 +17000,17 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17032,17 +17032,17 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -17064,17 +17064,17 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17096,17 +17096,17 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17128,17 +17128,17 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17155,22 +17155,22 @@
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中信恒业</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中源恒业</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17192,17 +17192,17 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17219,7 +17219,7 @@
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17256,17 +17256,17 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17288,17 +17288,17 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17320,17 +17320,17 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17352,17 +17352,17 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17384,17 +17384,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17416,17 +17416,17 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17448,17 +17448,17 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17480,17 +17480,17 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17512,17 +17512,17 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17544,17 +17544,17 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -17571,7 +17571,7 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
@@ -17581,12 +17581,12 @@
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道服务中心</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17608,17 +17608,17 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17640,17 +17640,17 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17667,22 +17667,22 @@
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17704,17 +17704,17 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17731,22 +17731,22 @@
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17768,17 +17768,17 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17795,22 +17795,22 @@
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17832,17 +17832,17 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17864,17 +17864,17 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道服务中心</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17896,17 +17896,17 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17928,17 +17928,17 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17960,17 +17960,17 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -17992,17 +17992,17 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18024,17 +18024,17 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18056,17 +18056,17 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18088,17 +18088,17 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18120,17 +18120,17 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -18147,22 +18147,22 @@
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18184,17 +18184,17 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -18216,17 +18216,17 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18248,17 +18248,17 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -18280,17 +18280,17 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -18312,17 +18312,17 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -18344,17 +18344,17 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -18371,22 +18371,22 @@
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -18413,12 +18413,12 @@
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -18440,17 +18440,17 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -18467,7 +18467,7 @@
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B169" s="5" t="inlineStr">
@@ -18477,12 +18477,12 @@
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -18509,12 +18509,12 @@
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -18536,17 +18536,17 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -18568,17 +18568,17 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
@@ -18728,17 +18728,17 @@
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
@@ -18748,29 +18748,29 @@
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>潍坊易豪4S中心</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>潍坊鑫易豪4S中心</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
@@ -18780,7 +18780,7 @@
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
@@ -18792,17 +18792,17 @@
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
+          <t>小米汽车兴义市桔康路授权服务中心</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
+          <t>小米汽车兴义市桔康路服务中心</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
@@ -18812,7 +18812,7 @@
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 91%</t>
         </is>
       </c>
     </row>
@@ -18824,17 +18824,17 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
@@ -18856,17 +18856,17 @@
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
@@ -18876,7 +18876,7 @@
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18888,17 +18888,17 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西萍乡安源区萍乡天虹</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
@@ -18908,29 +18908,29 @@
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>潍坊易豪4S中心</t>
+          <t>小米汽车天津西青区卫津南路授权服务中心</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>潍坊鑫易豪4S中心</t>
+          <t>小米汽车天津西青区卫津南路服务中心</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
@@ -18940,7 +18940,7 @@
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18952,17 +18952,17 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
@@ -18984,17 +18984,17 @@
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -19016,17 +19016,17 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路授权服务中心</t>
+          <t>小米汽车江西萍乡安源区萍乡天虹</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路服务中心</t>
+          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
@@ -19036,7 +19036,7 @@
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -19048,17 +19048,17 @@
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路授权服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 91%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -10326,7 +10326,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区永川万达</t>
+          <t>小米汽车重庆市江津区爱情海购物广场</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>中国重庆市永川区星光大道789号永川万达</t>
+          <t>重庆市江津区爱情海购物广场L1层中庭</t>
         </is>
       </c>
     </row>
@@ -10353,7 +10353,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市江津区爱情海购物广场</t>
+          <t>小米汽车重庆市永川区永川万达</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>重庆市江津区爱情海购物广场L1层中庭</t>
+          <t>中国重庆市永川区星光大道789号永川万达</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春中东新天地零售中心</t>
+          <t>理想汽车长春华润万象城零售中心</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区亚泰大街1138号</t>
+          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
         </is>
       </c>
     </row>
@@ -10569,7 +10569,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春华润万象城零售中心</t>
+          <t>理想汽车长春中东新天地零售中心</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
+          <t>吉林省长春市南关区亚泰大街1138号</t>
         </is>
       </c>
     </row>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>理想汽车潍坊寿光授权钣喷中心（广宝店）</t>
+          <t>理想汽车潍坊青州汽车园零售展厅</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>山东省潍坊市寿光市文家街道圣城西街666号</t>
+          <t>青州市玲珑山北路2359号</t>
         </is>
       </c>
     </row>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>理想汽车潍坊青州汽车园零售展厅</t>
+          <t>理想汽车潍坊寿光授权钣喷中心（广宝店）</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>青州市玲珑山北路2359号</t>
+          <t>山东省潍坊市寿光市文家街道圣城西街666号</t>
         </is>
       </c>
     </row>
@@ -10893,7 +10893,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南西城龙湖天街广场</t>
+          <t>蔚来空间 | 济南世纪大道万达广场</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
+          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
         </is>
       </c>
     </row>
@@ -10920,7 +10920,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南世纪大道万达广场</t>
+          <t>蔚来空间 | 济南西城龙湖天街广场</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
+          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•成都惠王陵西路</t>
+          <t>鸿蒙智行智界用户中心•成都武侯大道</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市龙泉驿区惠王陵西路155号</t>
+          <t>四川省成都市武侯区武侯大道顺江段61号</t>
         </is>
       </c>
     </row>
@@ -11055,7 +11055,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•成都武侯大道</t>
+          <t>鸿蒙智行尚界用户中心•成都惠王陵西路</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市武侯区武侯大道顺江段61号</t>
+          <t>四川省成都市龙泉驿区惠王陵西路155号</t>
         </is>
       </c>
     </row>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>理想汽车江门江海零售中心</t>
+          <t>理想汽车江门江海服务中心（利生车城店）</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>江门市江海区银帆路2号5幢-2</t>
+          <t>广东省江门市江海区银帆路2号5幢(利生车城)</t>
         </is>
       </c>
     </row>
@@ -11805,7 +11805,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>理想汽车江门江海服务中心（利生车城店）</t>
+          <t>理想汽车江门江海零售中心</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>广东省江门市江海区银帆路2号5幢(利生车城)</t>
+          <t>江门市江海区银帆路2号5幢-2</t>
         </is>
       </c>
     </row>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江服务中心（振兴东路店）</t>
+          <t>理想汽车衢州吾悦广场零售中心</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>衢州市衢江区振兴东路599号</t>
+          <t>浙江省衢州市柯城区白云中大道路99号吾悦广场1019-1商铺理想汽车</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>理想汽车衢州吾悦广场零售中心</t>
+          <t>理想汽车衢州衢江服务中心（振兴东路店）</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区白云中大道路99号吾悦广场1019-1商铺理想汽车</t>
+          <t>衢州市衢江区振兴东路599号</t>
         </is>
       </c>
     </row>
@@ -12075,7 +12075,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-罗湖卫星展厅</t>
+          <t>深圳中升悦晟-福田电气化体验馆</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
+          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
         </is>
       </c>
     </row>
@@ -12102,7 +12102,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-福田电气化体验馆</t>
+          <t>深圳中升悦晟-罗湖卫星展厅</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
+          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
         </is>
       </c>
     </row>
@@ -12480,7 +12480,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛乐客城</t>
+          <t>华为智能生活馆•青岛凯德Mall</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
+          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛凯德Mall</t>
+          <t>华为智能生活馆•青岛乐客城</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
+          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -13123,22 +13123,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13148,29 +13148,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
+          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13180,29 +13180,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13212,29 +13212,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
         </is>
       </c>
     </row>
@@ -13256,17 +13256,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13276,29 +13276,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
+          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13308,29 +13308,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13340,29 +13340,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13372,29 +13372,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13404,29 +13404,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
+          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13436,29 +13436,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
+          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13468,29 +13468,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13500,29 +13500,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13532,29 +13532,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13564,29 +13564,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13596,29 +13596,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>广东省珠海市香洲区前山工业区华威路103号A-23号 → 广东省珠海市香洲区前山工业区华威路103号二手车车库103-A-23号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
@@ -13672,17 +13672,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13692,29 +13692,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
@@ -13768,17 +13768,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13788,7 +13788,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
@@ -13800,17 +13800,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13820,29 +13820,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
+          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13852,29 +13852,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
         </is>
       </c>
     </row>
@@ -13896,17 +13896,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
+          <t>广东省珠海市香洲区前山工业区华威路103号A-23号 → 广东省珠海市香洲区前山工业区华威路103号二手车车库103-A-23号</t>
         </is>
       </c>
     </row>
@@ -13928,17 +13928,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
@@ -13960,17 +13960,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13980,14 +13980,14 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -13997,12 +13997,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14012,29 +14012,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14044,29 +14044,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
+          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14076,29 +14076,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14108,7 +14108,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
         </is>
       </c>
     </row>
@@ -14147,22 +14147,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
+          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
         </is>
       </c>
     </row>
@@ -14216,17 +14216,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14248,17 +14248,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14280,17 +14280,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14312,17 +14312,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14344,17 +14344,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14376,17 +14376,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14408,17 +14408,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14440,17 +14440,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14472,17 +14472,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14504,17 +14504,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14536,17 +14536,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14568,17 +14568,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14600,17 +14600,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14632,17 +14632,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14669,12 +14669,12 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14696,17 +14696,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14728,17 +14728,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14760,17 +14760,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14792,17 +14792,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14824,17 +14824,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14851,22 +14851,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14888,17 +14888,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14920,17 +14920,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14952,17 +14952,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14984,17 +14984,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15016,17 +15016,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15043,22 +15043,22 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>牡丹江中信恒业</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>牡丹江中源恒业</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15080,17 +15080,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15112,17 +15112,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15149,12 +15149,12 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15171,22 +15171,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中信恒业</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中源恒业</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15208,17 +15208,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15240,17 +15240,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15272,17 +15272,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15304,17 +15304,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15373,12 +15373,12 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15405,12 +15405,12 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15464,17 +15464,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15496,17 +15496,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15528,17 +15528,17 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15555,22 +15555,22 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15592,17 +15592,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15624,17 +15624,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15656,17 +15656,17 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -15688,17 +15688,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15720,17 +15720,17 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15752,17 +15752,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15784,17 +15784,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15821,12 +15821,12 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15848,17 +15848,17 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15880,17 +15880,17 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15907,22 +15907,22 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15944,17 +15944,17 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15976,17 +15976,17 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16008,17 +16008,17 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16035,22 +16035,22 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16072,17 +16072,17 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -16104,17 +16104,17 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16136,17 +16136,17 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16168,17 +16168,17 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16200,17 +16200,17 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -16232,17 +16232,17 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16269,12 +16269,12 @@
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16296,17 +16296,17 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16323,22 +16323,22 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16365,12 +16365,12 @@
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16392,17 +16392,17 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16424,17 +16424,17 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -16456,17 +16456,17 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16488,17 +16488,17 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16520,17 +16520,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16547,22 +16547,22 @@
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16584,17 +16584,17 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16611,22 +16611,22 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16643,22 +16643,22 @@
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -16680,17 +16680,17 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16707,22 +16707,22 @@
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车广东河源市源城区河源大道服务中心</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16744,17 +16744,17 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -16776,17 +16776,17 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16808,17 +16808,17 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16840,17 +16840,17 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -16872,17 +16872,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16909,12 +16909,12 @@
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16936,17 +16936,17 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16968,17 +16968,17 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -17000,17 +17000,17 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17032,17 +17032,17 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -17059,22 +17059,22 @@
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17096,17 +17096,17 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17128,17 +17128,17 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17160,17 +17160,17 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17192,17 +17192,17 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17219,22 +17219,22 @@
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17261,12 +17261,12 @@
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17288,17 +17288,17 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17320,17 +17320,17 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17357,12 +17357,12 @@
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17384,17 +17384,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17416,17 +17416,17 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17448,17 +17448,17 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17480,17 +17480,17 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17512,17 +17512,17 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17544,17 +17544,17 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -17571,22 +17571,22 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17608,17 +17608,17 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17645,12 +17645,12 @@
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17667,22 +17667,22 @@
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17704,17 +17704,17 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17736,17 +17736,17 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17768,17 +17768,17 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17795,22 +17795,22 @@
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17832,17 +17832,17 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17864,17 +17864,17 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17896,17 +17896,17 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17928,17 +17928,17 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17955,22 +17955,22 @@
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -17992,17 +17992,17 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18024,17 +18024,17 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18056,17 +18056,17 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18088,17 +18088,17 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18120,17 +18120,17 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -18152,17 +18152,17 @@
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18184,17 +18184,17 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -18216,17 +18216,17 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18248,17 +18248,17 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -18275,22 +18275,22 @@
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -18312,17 +18312,17 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -18344,17 +18344,17 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -18371,22 +18371,22 @@
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -18408,17 +18408,17 @@
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -18440,17 +18440,17 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -18472,17 +18472,17 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -18504,17 +18504,17 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -18536,17 +18536,17 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -18568,17 +18568,17 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
@@ -18595,22 +18595,22 @@
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•威海青岛南路</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
@@ -18620,29 +18620,29 @@
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 69%</t>
+          <t>地址相似度 88%</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
+          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
+          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
@@ -18652,29 +18652,29 @@
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 60%</t>
+          <t>地址相似度 88%</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
+          <t>鸿蒙智行尚界用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
+          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
@@ -18684,29 +18684,29 @@
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 88%</t>
+          <t>地址相似度 69%</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
+          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
+          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
@@ -18716,29 +18716,29 @@
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 88%</t>
+          <t>地址相似度 60%</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>潍坊易豪4S中心</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>潍坊鑫易豪4S中心</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
@@ -18748,29 +18748,29 @@
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>潍坊易豪4S中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>潍坊鑫易豪4S中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
@@ -18780,7 +18780,7 @@
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18792,17 +18792,17 @@
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路授权服务中心</t>
+          <t>小米汽车江西萍乡安源区萍乡天虹</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路服务中心</t>
+          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
@@ -18812,7 +18812,7 @@
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 91%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18824,17 +18824,17 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
@@ -18888,17 +18888,17 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
@@ -18920,17 +18920,17 @@
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路授权服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
@@ -18940,7 +18940,7 @@
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18952,17 +18952,17 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
@@ -18972,7 +18972,7 @@
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18984,17 +18984,17 @@
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
+          <t>小米汽车天津西青区卫津南路授权服务中心</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
+          <t>小米汽车天津西青区卫津南路服务中心</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -19016,17 +19016,17 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西萍乡安源区萍乡天虹</t>
+          <t>小米汽车兴义市桔康路授权服务中心</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
+          <t>小米汽车兴义市桔康路服务中心</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
@@ -19036,7 +19036,7 @@
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 91%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -10542,7 +10542,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春华润万象城零售中心</t>
+          <t>理想汽车长春中东新天地零售中心</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
+          <t>吉林省长春市南关区亚泰大街1138号</t>
         </is>
       </c>
     </row>
@@ -10569,7 +10569,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春中东新天地零售中心</t>
+          <t>理想汽车长春华润万象城零售中心</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区亚泰大街1138号</t>
+          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
         </is>
       </c>
     </row>
@@ -10893,7 +10893,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南世纪大道万达广场</t>
+          <t>蔚来空间 | 济南西城龙湖天街广场</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
+          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
         </is>
       </c>
     </row>
@@ -10920,7 +10920,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南西城龙湖天街广场</t>
+          <t>蔚来空间 | 济南世纪大道万达广场</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
+          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
         </is>
       </c>
     </row>
@@ -12210,7 +12210,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京王四营</t>
+          <t>华为智能生活馆•北京颐堤港</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营339号</t>
+          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
         </is>
       </c>
     </row>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京颐堤港</t>
+          <t>鸿蒙智行授权用户中心•北京王四营</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
+          <t>北京市朝阳区王四营339号</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（西田城）</t>
+          <t>华为授权体验店（南湖天地）</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
+          <t>浙江省嘉兴市南湖区南湖街道171号</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（星河COCOCity）</t>
+          <t>华为授权体验店（西田城）</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
+          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
         </is>
       </c>
     </row>
@@ -12804,7 +12804,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（南湖天地）</t>
+          <t>华为授权体验店（星河COCOCity）</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区南湖街道171号</t>
+          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
         </is>
       </c>
     </row>
@@ -13123,22 +13123,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13148,29 +13148,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13180,29 +13180,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13212,29 +13212,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
@@ -13256,17 +13256,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13276,29 +13276,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
+          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13308,29 +13308,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
+          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13340,7 +13340,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
         </is>
       </c>
     </row>
@@ -13384,17 +13384,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
@@ -13416,17 +13416,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13436,29 +13436,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13468,29 +13468,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13500,14 +13500,14 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -13517,12 +13517,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13532,7 +13532,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
+          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
         </is>
       </c>
     </row>
@@ -13571,22 +13571,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13596,29 +13596,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13628,29 +13628,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
+          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
         </is>
       </c>
     </row>
@@ -13672,17 +13672,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13692,29 +13692,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
         </is>
       </c>
     </row>
@@ -13736,17 +13736,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13756,29 +13756,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
+          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13788,29 +13788,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13820,29 +13820,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13852,7 +13852,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
@@ -13928,17 +13928,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13948,29 +13948,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13980,29 +13980,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
+          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14012,7 +14012,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
@@ -14024,17 +14024,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14044,7 +14044,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
+          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
         </is>
       </c>
     </row>
@@ -14056,17 +14056,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14076,29 +14076,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14108,29 +14108,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
+          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14140,29 +14140,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
@@ -14216,17 +14216,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14248,17 +14248,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14280,17 +14280,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14307,22 +14307,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14344,17 +14344,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14376,17 +14376,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14403,22 +14403,22 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14440,17 +14440,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14472,17 +14472,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14504,17 +14504,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14536,17 +14536,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14573,12 +14573,12 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14600,17 +14600,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14632,17 +14632,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14664,17 +14664,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14696,17 +14696,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14728,17 +14728,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14760,17 +14760,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14792,17 +14792,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14824,17 +14824,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14851,22 +14851,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14888,17 +14888,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14920,17 +14920,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14957,12 +14957,12 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14984,17 +14984,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15016,17 +15016,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15043,22 +15043,22 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中信恒业</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中源恒业</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15075,22 +15075,22 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15112,17 +15112,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15149,12 +15149,12 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15176,17 +15176,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15208,17 +15208,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15240,17 +15240,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15272,17 +15272,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15304,17 +15304,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15331,22 +15331,22 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15368,17 +15368,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15395,22 +15395,22 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15432,17 +15432,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -15464,17 +15464,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15496,17 +15496,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15528,17 +15528,17 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15555,22 +15555,22 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15592,17 +15592,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15624,17 +15624,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15656,17 +15656,17 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -15688,17 +15688,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15715,22 +15715,22 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15752,17 +15752,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15784,17 +15784,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15816,17 +15816,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15848,17 +15848,17 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15880,17 +15880,17 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15912,17 +15912,17 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15944,17 +15944,17 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15976,17 +15976,17 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16008,17 +16008,17 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16035,7 +16035,7 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
@@ -16045,12 +16045,12 @@
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16072,17 +16072,17 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -16104,17 +16104,17 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16136,17 +16136,17 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16168,17 +16168,17 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16200,17 +16200,17 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -16232,17 +16232,17 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16264,17 +16264,17 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16296,17 +16296,17 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16323,22 +16323,22 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16360,17 +16360,17 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16392,17 +16392,17 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16456,17 +16456,17 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16488,17 +16488,17 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16520,17 +16520,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16552,17 +16552,17 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16584,17 +16584,17 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16611,22 +16611,22 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16643,22 +16643,22 @@
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -16675,22 +16675,22 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16712,17 +16712,17 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16739,22 +16739,22 @@
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -16776,17 +16776,17 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16808,17 +16808,17 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16835,22 +16835,22 @@
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>牡丹江中信恒业</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>牡丹江中源恒业</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -16872,17 +16872,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16904,17 +16904,17 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16936,17 +16936,17 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16968,17 +16968,17 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -17000,17 +17000,17 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17032,17 +17032,17 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -17059,22 +17059,22 @@
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17096,17 +17096,17 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17128,17 +17128,17 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17160,17 +17160,17 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17192,17 +17192,17 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17256,17 +17256,17 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17288,17 +17288,17 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17320,17 +17320,17 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17352,17 +17352,17 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17384,17 +17384,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17416,17 +17416,17 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17448,17 +17448,17 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17475,22 +17475,22 @@
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17507,22 +17507,22 @@
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17544,17 +17544,17 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -17576,17 +17576,17 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17608,17 +17608,17 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17640,17 +17640,17 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17667,22 +17667,22 @@
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17709,12 +17709,12 @@
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17731,22 +17731,22 @@
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17768,17 +17768,17 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17800,17 +17800,17 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17832,17 +17832,17 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17864,17 +17864,17 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17896,17 +17896,17 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17928,17 +17928,17 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17955,22 +17955,22 @@
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -17992,17 +17992,17 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18024,17 +18024,17 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18056,17 +18056,17 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18088,17 +18088,17 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18120,17 +18120,17 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -18152,17 +18152,17 @@
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18184,17 +18184,17 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -18216,17 +18216,17 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18248,17 +18248,17 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -18275,22 +18275,22 @@
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -18312,17 +18312,17 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -18339,22 +18339,22 @@
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -18376,17 +18376,17 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -18408,17 +18408,17 @@
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -18440,17 +18440,17 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -18472,17 +18472,17 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -18509,12 +18509,12 @@
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -18536,17 +18536,17 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -18563,22 +18563,22 @@
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
@@ -18627,22 +18627,22 @@
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
+          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
+          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
@@ -18652,29 +18652,29 @@
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 88%</t>
+          <t>地址相似度 60%</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•威海青岛南路</t>
+          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
+          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
@@ -18684,29 +18684,29 @@
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 69%</t>
+          <t>地址相似度 88%</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
+          <t>鸿蒙智行尚界用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
+          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
@@ -18716,29 +18716,29 @@
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 60%</t>
+          <t>地址相似度 69%</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>潍坊易豪4S中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>潍坊鑫易豪4S中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
@@ -18748,7 +18748,7 @@
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18760,17 +18760,17 @@
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
@@ -18792,17 +18792,17 @@
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西萍乡安源区萍乡天虹</t>
+          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
+          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
@@ -18824,17 +18824,17 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
+          <t>小米汽车天津西青区卫津南路授权服务中心</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
+          <t>小米汽车天津西青区卫津南路服务中心</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18888,17 +18888,17 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
+          <t>小米汽车兴义市桔康路授权服务中心</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
+          <t>小米汽车兴义市桔康路服务中心</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
@@ -18908,7 +18908,7 @@
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 91%</t>
         </is>
       </c>
     </row>
@@ -18920,17 +18920,17 @@
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
@@ -18947,22 +18947,22 @@
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
+          <t>潍坊易豪4S中心</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
+          <t>潍坊鑫易豪4S中心</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
@@ -18972,7 +18972,7 @@
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
@@ -18984,17 +18984,17 @@
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路授权服务中心</t>
+          <t>小米汽车江西萍乡安源区萍乡天虹</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路服务中心</t>
+          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -19016,17 +19016,17 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路授权服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
@@ -19036,7 +19036,7 @@
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 91%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -10083,7 +10083,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区西四环双林东路服务中心</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>双林东路8号万开基地二期B座</t>
+          <t>北京市大兴区大兴龙湖天街一层中庭</t>
         </is>
       </c>
     </row>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京丰台区西四环双林东路服务中心</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>北京市大兴区大兴龙湖天街一层中庭</t>
+          <t>双林东路8号万开基地二期B座</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市庐阳区万象汇</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>安徽省合肥市庐阳区庐阳万象汇1F1号门入口</t>
+          <t>东塘路80号合肥巢湖万达广场1F</t>
         </is>
       </c>
     </row>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>小米汽车安徽省合肥市庐阳区万象汇</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>东塘路80号合肥巢湖万达广场1F</t>
+          <t>安徽省合肥市庐阳区庐阳万象汇1F1号门入口</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市江津区爱情海购物广场</t>
+          <t>小米汽车重庆市永川区永川万达</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>重庆市江津区爱情海购物广场L1层中庭</t>
+          <t>中国重庆市永川区星光大道789号永川万达</t>
         </is>
       </c>
     </row>
@@ -10353,7 +10353,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区永川万达</t>
+          <t>小米汽车重庆市江津区爱情海购物广场</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>中国重庆市永川区星光大道789号永川万达</t>
+          <t>重庆市江津区爱情海购物广场L1层中庭</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春中东新天地零售中心</t>
+          <t>理想汽车长春华润万象城零售中心</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区亚泰大街1138号</t>
+          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
         </is>
       </c>
     </row>
@@ -10569,7 +10569,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春华润万象城零售中心</t>
+          <t>理想汽车长春中东新天地零售中心</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
+          <t>吉林省长春市南关区亚泰大街1138号</t>
         </is>
       </c>
     </row>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>理想汽车潍坊青州汽车园零售展厅</t>
+          <t>理想汽车潍坊寿光授权钣喷中心（广宝店）</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>青州市玲珑山北路2359号</t>
+          <t>山东省潍坊市寿光市文家街道圣城西街666号</t>
         </is>
       </c>
     </row>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>理想汽车潍坊寿光授权钣喷中心（广宝店）</t>
+          <t>理想汽车潍坊青州汽车园零售展厅</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>山东省潍坊市寿光市文家街道圣城西街666号</t>
+          <t>青州市玲珑山北路2359号</t>
         </is>
       </c>
     </row>
@@ -10893,7 +10893,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南西城龙湖天街广场</t>
+          <t>蔚来空间 | 济南世纪大道万达广场</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
+          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
         </is>
       </c>
     </row>
@@ -10920,7 +10920,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南世纪大道万达广场</t>
+          <t>蔚来空间 | 济南西城龙湖天街广场</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
+          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•北京房山城关</t>
+          <t>华为智能生活馆•北京龙湖长楹天街</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>北京市房山区城关街道顾八路一区2号</t>
+          <t>北京市朝阳区常通路1号院龙湖长楹天街东区一层B栋-2F-C32，B栋-1F-19a，B栋-2F-21，B栋-1F-19b，B栋-2F-19a，B栋-2F-19b，B栋-2F-20号商铺</t>
         </is>
       </c>
     </row>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京龙湖长楹天街</t>
+          <t>鸿蒙智行智界用户中心•北京房山城关</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通路1号院龙湖长楹天街东区一层B栋-2F-C32，B栋-1F-19a，B栋-2F-21，B栋-1F-19b，B栋-2F-19a，B栋-2F-19b，B栋-2F-20号商铺</t>
+          <t>北京市房山区城关街道顾八路一区2号</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•宁波下应</t>
+          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
+          <t>AITO授权用户中心•宁波下应</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（长楹龙湖）</t>
+          <t>华为智能生活馆•北京颐堤港</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
+          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
         </is>
       </c>
     </row>
@@ -12210,7 +12210,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京颐堤港</t>
+          <t>鸿蒙智行授权用户中心•北京王四营</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
+          <t>北京市朝阳区王四营339号</t>
         </is>
       </c>
     </row>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京王四营</t>
+          <t>华为授权体验店（长楹龙湖）</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营339号</t>
+          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（南湖天地）</t>
+          <t>华为授权体验店（西田城）</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区南湖街道171号</t>
+          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（西田城）</t>
+          <t>华为授权体验店（星河COCOCity）</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
+          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
         </is>
       </c>
     </row>
@@ -12804,7 +12804,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（星河COCOCity）</t>
+          <t>华为授权体验店（南湖天地）</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
+          <t>浙江省嘉兴市南湖区南湖街道171号</t>
         </is>
       </c>
     </row>
@@ -13128,17 +13128,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13148,29 +13148,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13180,29 +13180,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13212,29 +13212,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
+          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
@@ -13256,17 +13256,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13276,7 +13276,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
+          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
         </is>
       </c>
     </row>
@@ -13288,17 +13288,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13308,29 +13308,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13340,29 +13340,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13372,29 +13372,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
@@ -13416,17 +13416,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13436,29 +13436,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13468,29 +13468,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
+          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13500,14 +13500,14 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
+          <t>广东省珠海市香洲区前山工业区华威路103号A-23号 → 广东省珠海市香洲区前山工业区华威路103号二手车车库103-A-23号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -13517,12 +13517,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13532,29 +13532,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
+          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13564,29 +13564,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13596,29 +13596,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13628,29 +13628,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
+          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
+          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
         </is>
       </c>
     </row>
@@ -13672,17 +13672,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13692,7 +13692,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
@@ -13704,17 +13704,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
+          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
         </is>
       </c>
     </row>
@@ -13736,17 +13736,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13756,14 +13756,14 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -13773,12 +13773,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13788,29 +13788,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
+          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13820,29 +13820,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13852,29 +13852,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
@@ -13896,17 +13896,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13916,29 +13916,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>广东省珠海市香洲区前山工业区华威路103号A-23号 → 广东省珠海市香洲区前山工业区华威路103号二手车车库103-A-23号</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13948,29 +13948,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13980,29 +13980,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
+          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14012,29 +14012,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14044,7 +14044,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
+          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
         </is>
       </c>
     </row>
@@ -14056,17 +14056,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14076,29 +14076,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14108,7 +14108,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
+          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
         </is>
       </c>
     </row>
@@ -14125,12 +14125,12 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14140,7 +14140,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
@@ -14152,17 +14152,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
@@ -14216,17 +14216,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14248,17 +14248,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14280,17 +14280,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14307,22 +14307,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14344,17 +14344,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14376,17 +14376,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14403,22 +14403,22 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14440,17 +14440,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14472,17 +14472,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14504,17 +14504,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14536,17 +14536,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14568,17 +14568,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14595,22 +14595,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14632,17 +14632,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14664,17 +14664,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14691,22 +14691,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14728,17 +14728,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14760,17 +14760,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14787,22 +14787,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14824,17 +14824,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14856,17 +14856,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14883,22 +14883,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14920,17 +14920,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14952,17 +14952,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14984,17 +14984,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15016,17 +15016,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15048,17 +15048,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15075,22 +15075,22 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15112,17 +15112,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15144,17 +15144,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15176,17 +15176,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15208,17 +15208,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15240,17 +15240,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15272,17 +15272,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15304,17 +15304,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15331,22 +15331,22 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15368,17 +15368,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15400,17 +15400,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15432,17 +15432,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -15469,12 +15469,12 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15496,17 +15496,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15533,12 +15533,12 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15555,22 +15555,22 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15587,22 +15587,22 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15619,22 +15619,22 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15656,17 +15656,17 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -15688,17 +15688,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15752,17 +15752,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15784,17 +15784,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15816,17 +15816,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15848,17 +15848,17 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15880,17 +15880,17 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15917,12 +15917,12 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15944,17 +15944,17 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15976,17 +15976,17 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16008,17 +16008,17 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16035,22 +16035,22 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16072,17 +16072,17 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -16104,17 +16104,17 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16136,17 +16136,17 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16168,17 +16168,17 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16205,12 +16205,12 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -16232,17 +16232,17 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16264,17 +16264,17 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16296,17 +16296,17 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16328,17 +16328,17 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16365,12 +16365,12 @@
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16392,17 +16392,17 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16424,17 +16424,17 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -16456,17 +16456,17 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16488,17 +16488,17 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16520,17 +16520,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16552,17 +16552,17 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16579,22 +16579,22 @@
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16616,17 +16616,17 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16675,22 +16675,22 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16712,17 +16712,17 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16739,22 +16739,22 @@
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -16776,17 +16776,17 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16808,17 +16808,17 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16872,17 +16872,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16904,17 +16904,17 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16936,17 +16936,17 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16968,17 +16968,17 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -17005,12 +17005,12 @@
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17032,17 +17032,17 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -17064,17 +17064,17 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17091,22 +17091,22 @@
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17123,22 +17123,22 @@
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17160,17 +17160,17 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17192,17 +17192,17 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17224,17 +17224,17 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17256,17 +17256,17 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17288,17 +17288,17 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17325,12 +17325,12 @@
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17352,17 +17352,17 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17384,17 +17384,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17416,17 +17416,17 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17448,17 +17448,17 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17475,22 +17475,22 @@
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17507,22 +17507,22 @@
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17544,17 +17544,17 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -17576,17 +17576,17 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17608,17 +17608,17 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17640,17 +17640,17 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17672,17 +17672,17 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17704,17 +17704,17 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17736,17 +17736,17 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17768,17 +17768,17 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17800,17 +17800,17 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17832,17 +17832,17 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17864,17 +17864,17 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17896,17 +17896,17 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17928,17 +17928,17 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17960,17 +17960,17 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -17992,17 +17992,17 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18024,17 +18024,17 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18056,17 +18056,17 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18088,17 +18088,17 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18125,12 +18125,12 @@
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -18152,17 +18152,17 @@
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18184,17 +18184,17 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -18216,17 +18216,17 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道服务中心</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18248,17 +18248,17 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -18280,17 +18280,17 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -18312,17 +18312,17 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -18339,22 +18339,22 @@
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -18376,17 +18376,17 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -18408,17 +18408,17 @@
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -18440,17 +18440,17 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -18472,17 +18472,17 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -18504,17 +18504,17 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -18536,17 +18536,17 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -18563,22 +18563,22 @@
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
@@ -18595,22 +18595,22 @@
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
+          <t>鸿蒙智行尚界用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
+          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
@@ -18620,29 +18620,29 @@
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 88%</t>
+          <t>地址相似度 69%</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
+          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
+          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
@@ -18652,29 +18652,29 @@
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 60%</t>
+          <t>地址相似度 88%</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
+          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
+          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
@@ -18684,29 +18684,29 @@
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 88%</t>
+          <t>地址相似度 60%</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•威海青岛南路</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
@@ -18716,29 +18716,29 @@
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 69%</t>
+          <t>地址相似度 88%</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
+          <t>潍坊易豪4S中心</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
+          <t>潍坊鑫易豪4S中心</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
@@ -18748,7 +18748,7 @@
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
@@ -18792,17 +18792,17 @@
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
@@ -18812,7 +18812,7 @@
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18824,17 +18824,17 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路授权服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18856,17 +18856,17 @@
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
+          <t>小米汽车江西萍乡安源区萍乡天虹</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
+          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
@@ -18876,7 +18876,7 @@
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18888,17 +18888,17 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路授权服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
@@ -18908,7 +18908,7 @@
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 91%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18920,17 +18920,17 @@
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
@@ -18947,22 +18947,22 @@
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>潍坊易豪4S中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>潍坊鑫易豪4S中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
@@ -18972,7 +18972,7 @@
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18984,17 +18984,17 @@
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西萍乡安源区萍乡天虹</t>
+          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
+          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
@@ -19016,17 +19016,17 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>小米汽车天津西青区卫津南路授权服务中心</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>小米汽车天津西青区卫津南路服务中心</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
@@ -19036,7 +19036,7 @@
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -19048,17 +19048,17 @@
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
+          <t>小米汽车兴义市桔康路授权服务中心</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
+          <t>小米汽车兴义市桔康路服务中心</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 91%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -10083,7 +10083,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京丰台区西四环双林东路服务中心</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>北京市大兴区大兴龙湖天街一层中庭</t>
+          <t>双林东路8号万开基地二期B座</t>
         </is>
       </c>
     </row>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区西四环双林东路服务中心</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>双林东路8号万开基地二期B座</t>
+          <t>北京市大兴区大兴龙湖天街一层中庭</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>小米汽车安徽省合肥市庐阳区万象汇</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>东塘路80号合肥巢湖万达广场1F</t>
+          <t>安徽省合肥市庐阳区庐阳万象汇1F1号门入口</t>
         </is>
       </c>
     </row>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市庐阳区万象汇</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>安徽省合肥市庐阳区庐阳万象汇1F1号门入口</t>
+          <t>东塘路80号合肥巢湖万达广场1F</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春华润万象城零售中心</t>
+          <t>理想汽车长春中东新天地零售中心</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
+          <t>吉林省长春市南关区亚泰大街1138号</t>
         </is>
       </c>
     </row>
@@ -10569,7 +10569,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春中东新天地零售中心</t>
+          <t>理想汽车长春华润万象城零售中心</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区亚泰大街1138号</t>
+          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
         </is>
       </c>
     </row>
@@ -10893,7 +10893,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南世纪大道万达广场</t>
+          <t>蔚来空间 | 济南西城龙湖天街广场</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
+          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
         </is>
       </c>
     </row>
@@ -10920,7 +10920,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南西城龙湖天街广场</t>
+          <t>蔚来空间 | 济南世纪大道万达广场</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
+          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
         </is>
       </c>
     </row>
@@ -12075,7 +12075,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-福田电气化体验馆</t>
+          <t>深圳中升悦晟-罗湖卫星展厅</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
+          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
         </is>
       </c>
     </row>
@@ -12102,7 +12102,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-罗湖卫星展厅</t>
+          <t>深圳中升悦晟-福田电气化体验馆</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
+          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
         </is>
       </c>
     </row>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京颐堤港</t>
+          <t>鸿蒙智行授权用户中心•北京王四营</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
+          <t>北京市朝阳区王四营339号</t>
         </is>
       </c>
     </row>
@@ -12210,7 +12210,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京王四营</t>
+          <t>华为授权体验店（长楹龙湖）</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营339号</t>
+          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
         </is>
       </c>
     </row>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（长楹龙湖）</t>
+          <t>华为智能生活馆•北京颐堤港</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
+          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
         </is>
       </c>
     </row>
@@ -12480,7 +12480,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛凯德Mall</t>
+          <t>华为智能生活馆•青岛乐客城</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
+          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛乐客城</t>
+          <t>华为智能生活馆•青岛凯德Mall</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
+          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（西田城）</t>
+          <t>华为授权体验店（南湖天地）</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
+          <t>浙江省嘉兴市南湖区南湖街道171号</t>
         </is>
       </c>
     </row>
@@ -12804,7 +12804,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（南湖天地）</t>
+          <t>华为授权体验店（西田城）</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区南湖街道171号</t>
+          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
         </is>
       </c>
     </row>
@@ -13123,22 +13123,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13148,29 +13148,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
+          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13180,29 +13180,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13212,29 +13212,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13244,29 +13244,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13276,7 +13276,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
         </is>
       </c>
     </row>
@@ -13288,17 +13288,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13308,29 +13308,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13340,29 +13340,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13372,29 +13372,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13404,29 +13404,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13436,29 +13436,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
@@ -13480,17 +13480,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13500,14 +13500,14 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>广东省珠海市香洲区前山工业区华威路103号A-23号 → 广东省珠海市香洲区前山工业区华威路103号二手车车库103-A-23号</t>
+          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -13517,12 +13517,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13532,29 +13532,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
+          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13564,7 +13564,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>广东省珠海市香洲区前山工业区华威路103号A-23号 → 广东省珠海市香洲区前山工业区华威路103号二手车车库103-A-23号</t>
         </is>
       </c>
     </row>
@@ -13576,17 +13576,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13596,29 +13596,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13628,29 +13628,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13660,29 +13660,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
+          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13692,29 +13692,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
+          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
         </is>
       </c>
     </row>
@@ -13736,17 +13736,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
         </is>
       </c>
     </row>
@@ -13768,17 +13768,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13788,29 +13788,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
+          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13820,29 +13820,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13852,29 +13852,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
@@ -13896,17 +13896,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13916,29 +13916,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13948,29 +13948,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13980,29 +13980,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
+          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14012,7 +14012,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
+          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
         </is>
       </c>
     </row>
@@ -14056,17 +14056,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14076,29 +14076,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14108,7 +14108,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
@@ -14120,17 +14120,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14140,29 +14140,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
@@ -14216,17 +14216,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14248,17 +14248,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14280,17 +14280,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14312,17 +14312,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14344,17 +14344,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14371,22 +14371,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14408,17 +14408,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14440,17 +14440,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14472,17 +14472,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14504,17 +14504,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14536,17 +14536,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14573,12 +14573,12 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14595,22 +14595,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14632,17 +14632,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14659,22 +14659,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14691,22 +14691,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14728,17 +14728,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14760,17 +14760,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14787,22 +14787,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14824,17 +14824,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14856,17 +14856,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14883,22 +14883,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14920,17 +14920,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14952,17 +14952,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14984,17 +14984,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15016,17 +15016,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15048,17 +15048,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15080,17 +15080,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15112,17 +15112,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15149,12 +15149,12 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15176,17 +15176,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15208,17 +15208,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15240,17 +15240,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15272,17 +15272,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15304,17 +15304,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15331,22 +15331,22 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15368,17 +15368,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15400,17 +15400,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15432,17 +15432,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -15464,17 +15464,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15496,17 +15496,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15528,17 +15528,17 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15565,12 +15565,12 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15587,22 +15587,22 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15619,22 +15619,22 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15656,17 +15656,17 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -15688,17 +15688,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15715,22 +15715,22 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15752,17 +15752,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15784,17 +15784,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15816,17 +15816,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15880,17 +15880,17 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15907,22 +15907,22 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15949,12 +15949,12 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15976,17 +15976,17 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16008,17 +16008,17 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16040,17 +16040,17 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16072,17 +16072,17 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -16104,17 +16104,17 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16136,17 +16136,17 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16168,17 +16168,17 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16195,7 +16195,7 @@
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
@@ -16205,12 +16205,12 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -16232,17 +16232,17 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16264,17 +16264,17 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16296,17 +16296,17 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16328,17 +16328,17 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16360,17 +16360,17 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16392,17 +16392,17 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16424,17 +16424,17 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -16456,17 +16456,17 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16488,17 +16488,17 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16520,17 +16520,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16552,17 +16552,17 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16579,22 +16579,22 @@
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16616,17 +16616,17 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16648,17 +16648,17 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -16680,17 +16680,17 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16712,17 +16712,17 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16744,17 +16744,17 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -16776,17 +16776,17 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16808,17 +16808,17 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16835,22 +16835,22 @@
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中信恒业</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中源恒业</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -16872,17 +16872,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16904,17 +16904,17 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16936,17 +16936,17 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16968,17 +16968,17 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -17000,17 +17000,17 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17032,17 +17032,17 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -17064,17 +17064,17 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17091,22 +17091,22 @@
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17123,22 +17123,22 @@
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17160,17 +17160,17 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17187,22 +17187,22 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17224,17 +17224,17 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17256,17 +17256,17 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17288,17 +17288,17 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道服务中心</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17315,22 +17315,22 @@
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17352,17 +17352,17 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17384,17 +17384,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17421,12 +17421,12 @@
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17448,17 +17448,17 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17480,17 +17480,17 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17512,17 +17512,17 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17544,17 +17544,17 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -17571,22 +17571,22 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17608,17 +17608,17 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17640,17 +17640,17 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17672,17 +17672,17 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17704,17 +17704,17 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17736,17 +17736,17 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17768,17 +17768,17 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17800,17 +17800,17 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17827,22 +17827,22 @@
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17864,17 +17864,17 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17896,17 +17896,17 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17933,12 +17933,12 @@
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17960,17 +17960,17 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -17992,17 +17992,17 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18024,17 +18024,17 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18056,17 +18056,17 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18088,17 +18088,17 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18120,17 +18120,17 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -18147,22 +18147,22 @@
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18184,17 +18184,17 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -18216,17 +18216,17 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18243,22 +18243,22 @@
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -18275,22 +18275,22 @@
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
+          <t>牡丹江中信恒业</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
+          <t>牡丹江中源恒业</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -18307,22 +18307,22 @@
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -18339,22 +18339,22 @@
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -18376,17 +18376,17 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -18408,17 +18408,17 @@
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -18440,17 +18440,17 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -18472,17 +18472,17 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -18504,17 +18504,17 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -18536,17 +18536,17 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -18573,12 +18573,12 @@
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
@@ -18595,22 +18595,22 @@
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•威海青岛南路</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
@@ -18620,7 +18620,7 @@
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 69%</t>
+          <t>地址相似度 88%</t>
         </is>
       </c>
     </row>
@@ -18659,22 +18659,22 @@
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
+          <t>鸿蒙智行尚界用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
+          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
@@ -18684,29 +18684,29 @@
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 60%</t>
+          <t>地址相似度 69%</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
+          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
+          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
@@ -18716,29 +18716,29 @@
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 88%</t>
+          <t>地址相似度 60%</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>潍坊易豪4S中心</t>
+          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>潍坊鑫易豪4S中心</t>
+          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
@@ -18748,7 +18748,7 @@
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18760,17 +18760,17 @@
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
+          <t>小米汽车兴义市桔康路授权服务中心</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
+          <t>小米汽车兴义市桔康路服务中心</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
@@ -18780,7 +18780,7 @@
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 91%</t>
         </is>
       </c>
     </row>
@@ -18792,17 +18792,17 @@
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
+          <t>小米汽车天津西青区卫津南路授权服务中心</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
+          <t>小米汽车天津西青区卫津南路服务中心</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
@@ -18824,17 +18824,17 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18856,17 +18856,17 @@
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西萍乡安源区萍乡天虹</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
@@ -18888,17 +18888,17 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
@@ -18908,29 +18908,29 @@
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>潍坊易豪4S中心</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>潍坊鑫易豪4S中心</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
@@ -18940,7 +18940,7 @@
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
@@ -18952,17 +18952,17 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
@@ -18984,17 +18984,17 @@
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -19016,17 +19016,17 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路授权服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
@@ -19036,7 +19036,7 @@
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -19048,17 +19048,17 @@
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路授权服务中心</t>
+          <t>小米汽车江西萍乡安源区萍乡天虹</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路服务中心</t>
+          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 91%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -10542,7 +10542,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春中东新天地零售中心</t>
+          <t>理想汽车长春华润万象城零售中心</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区亚泰大街1138号</t>
+          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
         </is>
       </c>
     </row>
@@ -10569,7 +10569,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春华润万象城零售中心</t>
+          <t>理想汽车长春中东新天地零售中心</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
+          <t>吉林省长春市南关区亚泰大街1138号</t>
         </is>
       </c>
     </row>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>理想汽车潍坊寿光授权钣喷中心（广宝店）</t>
+          <t>理想汽车潍坊青州汽车园零售展厅</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>山东省潍坊市寿光市文家街道圣城西街666号</t>
+          <t>青州市玲珑山北路2359号</t>
         </is>
       </c>
     </row>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>理想汽车潍坊青州汽车园零售展厅</t>
+          <t>理想汽车潍坊寿光授权钣喷中心（广宝店）</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>青州市玲珑山北路2359号</t>
+          <t>山东省潍坊市寿光市文家街道圣城西街666号</t>
         </is>
       </c>
     </row>
@@ -10893,7 +10893,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南西城龙湖天街广场</t>
+          <t>蔚来空间 | 济南世纪大道万达广场</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
+          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
         </is>
       </c>
     </row>
@@ -10920,7 +10920,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南世纪大道万达广场</t>
+          <t>蔚来空间 | 济南西城龙湖天街广场</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
+          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京龙湖长楹天街</t>
+          <t>鸿蒙智行智界用户中心•北京房山城关</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通路1号院龙湖长楹天街东区一层B栋-2F-C32，B栋-1F-19a，B栋-2F-21，B栋-1F-19b，B栋-2F-19a，B栋-2F-19b，B栋-2F-20号商铺</t>
+          <t>北京市房山区城关街道顾八路一区2号</t>
         </is>
       </c>
     </row>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•北京房山城关</t>
+          <t>华为智能生活馆•北京龙湖长楹天街</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>北京市房山区城关街道顾八路一区2号</t>
+          <t>北京市朝阳区常通路1号院龙湖长楹天街东区一层B栋-2F-C32，B栋-1F-19a，B栋-2F-21，B栋-1F-19b，B栋-2F-19a，B栋-2F-19b，B栋-2F-20号商铺</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
+          <t>AITO授权用户中心•宁波下应</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•宁波下应</t>
+          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -12075,7 +12075,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-罗湖卫星展厅</t>
+          <t>深圳中升悦晟-福田电气化体验馆</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
+          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
         </is>
       </c>
     </row>
@@ -12102,7 +12102,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-福田电气化体验馆</t>
+          <t>深圳中升悦晟-罗湖卫星展厅</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
+          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
         </is>
       </c>
     </row>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京王四营</t>
+          <t>华为授权体验店（长楹龙湖）</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营339号</t>
+          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
         </is>
       </c>
     </row>
@@ -12210,7 +12210,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（长楹龙湖）</t>
+          <t>鸿蒙智行授权用户中心•北京王四营</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
+          <t>北京市朝阳区王四营339号</t>
         </is>
       </c>
     </row>
@@ -12480,7 +12480,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛乐客城</t>
+          <t>华为智能生活馆•青岛凯德Mall</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
+          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛凯德Mall</t>
+          <t>华为智能生活馆•青岛乐客城</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
+          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -13123,22 +13123,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13148,29 +13148,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
         </is>
       </c>
     </row>
@@ -13192,17 +13192,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13212,29 +13212,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13244,29 +13244,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13276,7 +13276,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
@@ -13288,17 +13288,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13308,29 +13308,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13340,29 +13340,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13372,29 +13372,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
+          <t>广东省珠海市香洲区前山工业区华威路103号A-23号 → 广东省珠海市香洲区前山工业区华威路103号二手车车库103-A-23号</t>
         </is>
       </c>
     </row>
@@ -13416,17 +13416,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13436,29 +13436,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
+          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
         </is>
       </c>
     </row>
@@ -13480,17 +13480,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13500,29 +13500,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13532,29 +13532,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13564,29 +13564,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省珠海市香洲区前山工业区华威路103号A-23号 → 广东省珠海市香洲区前山工业区华威路103号二手车车库103-A-23号</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13596,29 +13596,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13628,29 +13628,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
@@ -13699,22 +13699,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
@@ -13736,17 +13736,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
+          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
         </is>
       </c>
     </row>
@@ -13768,17 +13768,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13788,29 +13788,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
+          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13820,29 +13820,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
+          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13852,7 +13852,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
@@ -13869,12 +13869,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13884,29 +13884,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
+          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
         </is>
       </c>
     </row>
@@ -13928,17 +13928,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13948,29 +13948,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13980,29 +13980,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14012,29 +14012,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14044,29 +14044,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14076,29 +14076,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14108,7 +14108,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
@@ -14120,17 +14120,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14140,29 +14140,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
         </is>
       </c>
     </row>
@@ -14216,17 +14216,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14248,17 +14248,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14280,17 +14280,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14312,17 +14312,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14344,17 +14344,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14371,22 +14371,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14413,12 +14413,12 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14440,17 +14440,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14472,17 +14472,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14499,22 +14499,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14531,22 +14531,22 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14568,17 +14568,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14595,7 +14595,7 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -14605,12 +14605,12 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14632,17 +14632,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14659,22 +14659,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14696,17 +14696,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14728,17 +14728,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14760,17 +14760,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14792,17 +14792,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14824,17 +14824,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14856,17 +14856,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14888,17 +14888,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14920,17 +14920,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14952,17 +14952,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14979,22 +14979,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15016,17 +15016,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15048,17 +15048,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15080,17 +15080,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15112,17 +15112,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15144,17 +15144,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15176,17 +15176,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15208,17 +15208,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15240,17 +15240,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15272,17 +15272,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15304,17 +15304,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15331,22 +15331,22 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15368,17 +15368,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15395,7 +15395,7 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
@@ -15405,12 +15405,12 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15432,17 +15432,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -15459,22 +15459,22 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15496,17 +15496,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15528,17 +15528,17 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15560,17 +15560,17 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15592,17 +15592,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15624,17 +15624,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道服务中心</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15656,17 +15656,17 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -15688,17 +15688,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15720,17 +15720,17 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15752,17 +15752,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15784,17 +15784,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15816,17 +15816,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15848,17 +15848,17 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15880,17 +15880,17 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15907,22 +15907,22 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15944,17 +15944,17 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15976,17 +15976,17 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16008,17 +16008,17 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16040,17 +16040,17 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16072,17 +16072,17 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -16104,17 +16104,17 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16136,17 +16136,17 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16168,17 +16168,17 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16195,22 +16195,22 @@
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -16232,17 +16232,17 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16264,17 +16264,17 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16296,17 +16296,17 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16328,17 +16328,17 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16360,17 +16360,17 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16392,17 +16392,17 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16419,22 +16419,22 @@
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -16456,17 +16456,17 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16488,17 +16488,17 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16520,17 +16520,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16552,17 +16552,17 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16584,17 +16584,17 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16616,17 +16616,17 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16648,17 +16648,17 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -16680,17 +16680,17 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16712,17 +16712,17 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16744,17 +16744,17 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -16771,22 +16771,22 @@
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16808,17 +16808,17 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16840,17 +16840,17 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -16877,12 +16877,12 @@
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16904,17 +16904,17 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16936,17 +16936,17 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16968,17 +16968,17 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -17000,17 +17000,17 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17032,17 +17032,17 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -17064,17 +17064,17 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17096,17 +17096,17 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17128,17 +17128,17 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17160,17 +17160,17 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17187,22 +17187,22 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17219,22 +17219,22 @@
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17256,17 +17256,17 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17288,17 +17288,17 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17315,22 +17315,22 @@
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17352,17 +17352,17 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17384,17 +17384,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17416,17 +17416,17 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17448,17 +17448,17 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17480,17 +17480,17 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17512,17 +17512,17 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17539,22 +17539,22 @@
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -17571,22 +17571,22 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17608,17 +17608,17 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17640,17 +17640,17 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17672,17 +17672,17 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17699,22 +17699,22 @@
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17736,17 +17736,17 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17768,17 +17768,17 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17800,17 +17800,17 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17827,22 +17827,22 @@
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17864,17 +17864,17 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17896,17 +17896,17 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17928,17 +17928,17 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17960,17 +17960,17 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -17992,17 +17992,17 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18024,17 +18024,17 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18061,12 +18061,12 @@
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18083,22 +18083,22 @@
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>牡丹江中信恒业</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>牡丹江中源恒业</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18120,17 +18120,17 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -18147,22 +18147,22 @@
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18184,17 +18184,17 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -18216,17 +18216,17 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18243,22 +18243,22 @@
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -18275,22 +18275,22 @@
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中信恒业</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中源恒业</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -18307,22 +18307,22 @@
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -18344,17 +18344,17 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -18376,17 +18376,17 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -18408,17 +18408,17 @@
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -18435,7 +18435,7 @@
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
@@ -18445,12 +18445,12 @@
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -18472,17 +18472,17 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -18504,17 +18504,17 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -18536,17 +18536,17 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -18568,17 +18568,17 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
@@ -18627,22 +18627,22 @@
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
+          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
+          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
@@ -18652,7 +18652,7 @@
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 88%</t>
+          <t>地址相似度 60%</t>
         </is>
       </c>
     </row>
@@ -18691,22 +18691,22 @@
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
+          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
+          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
@@ -18716,29 +18716,29 @@
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 60%</t>
+          <t>地址相似度 88%</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
+          <t>潍坊易豪4S中心</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
+          <t>潍坊鑫易豪4S中心</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
@@ -18748,7 +18748,7 @@
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
@@ -18760,17 +18760,17 @@
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路授权服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
@@ -18780,7 +18780,7 @@
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 91%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18792,17 +18792,17 @@
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路授权服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
@@ -18812,7 +18812,7 @@
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18824,17 +18824,17 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
+          <t>小米汽车天津西青区卫津南路授权服务中心</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
+          <t>小米汽车天津西青区卫津南路服务中心</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18856,17 +18856,17 @@
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
@@ -18876,7 +18876,7 @@
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18888,17 +18888,17 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
+          <t>小米汽车江西萍乡安源区萍乡天虹</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
+          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
@@ -18915,22 +18915,22 @@
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>潍坊易豪4S中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>潍坊鑫易豪4S中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
@@ -18940,7 +18940,7 @@
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18952,17 +18952,17 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
@@ -18972,7 +18972,7 @@
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18984,17 +18984,17 @@
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
+          <t>小米汽车兴义市桔康路授权服务中心</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
+          <t>小米汽车兴义市桔康路服务中心</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 91%</t>
         </is>
       </c>
     </row>
@@ -19016,17 +19016,17 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
@@ -19048,17 +19048,17 @@
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西萍乡安源区萍乡天虹</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -10137,7 +10137,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市庐阳区万象汇</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>安徽省合肥市庐阳区庐阳万象汇1F1号门入口</t>
+          <t>东塘路80号合肥巢湖万达广场1F</t>
         </is>
       </c>
     </row>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>小米汽车安徽省合肥市庐阳区万象汇</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>东塘路80号合肥巢湖万达广场1F</t>
+          <t>安徽省合肥市庐阳区庐阳万象汇1F1号门入口</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春华润万象城零售中心</t>
+          <t>理想汽车长春中东新天地零售中心</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
+          <t>吉林省长春市南关区亚泰大街1138号</t>
         </is>
       </c>
     </row>
@@ -10569,7 +10569,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春中东新天地零售中心</t>
+          <t>理想汽车长春华润万象城零售中心</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区亚泰大街1138号</t>
+          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
         </is>
       </c>
     </row>
@@ -10893,7 +10893,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南世纪大道万达广场</t>
+          <t>蔚来空间 | 济南西城龙湖天街广场</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
+          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
         </is>
       </c>
     </row>
@@ -10920,7 +10920,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南西城龙湖天街广场</t>
+          <t>蔚来空间 | 济南世纪大道万达广场</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
+          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•北京房山城关</t>
+          <t>华为智能生活馆•北京龙湖长楹天街</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>北京市房山区城关街道顾八路一区2号</t>
+          <t>北京市朝阳区常通路1号院龙湖长楹天街东区一层B栋-2F-C32，B栋-1F-19a，B栋-2F-21，B栋-1F-19b，B栋-2F-19a，B栋-2F-19b，B栋-2F-20号商铺</t>
         </is>
       </c>
     </row>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京龙湖长楹天街</t>
+          <t>鸿蒙智行智界用户中心•北京房山城关</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通路1号院龙湖长楹天街东区一层B栋-2F-C32，B栋-1F-19a，B栋-2F-21，B栋-1F-19b，B栋-2F-19a，B栋-2F-19b，B栋-2F-20号商铺</t>
+          <t>北京市房山区城关街道顾八路一区2号</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•成都武侯大道</t>
+          <t>鸿蒙智行尚界用户中心•成都惠王陵西路</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市武侯区武侯大道顺江段61号</t>
+          <t>四川省成都市龙泉驿区惠王陵西路155号</t>
         </is>
       </c>
     </row>
@@ -11055,7 +11055,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•成都惠王陵西路</t>
+          <t>鸿蒙智行智界用户中心•成都武侯大道</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市龙泉驿区惠王陵西路155号</t>
+          <t>四川省成都市武侯区武侯大道顺江段61号</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•宁波下应</t>
+          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
+          <t>AITO授权用户中心•宁波下应</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>理想汽车江门江海服务中心（利生车城店）</t>
+          <t>理想汽车江门江海零售中心</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>广东省江门市江海区银帆路2号5幢(利生车城)</t>
+          <t>江门市江海区银帆路2号5幢-2</t>
         </is>
       </c>
     </row>
@@ -11805,7 +11805,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>理想汽车江门江海零售中心</t>
+          <t>理想汽车江门江海服务中心（利生车城店）</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>江门市江海区银帆路2号5幢-2</t>
+          <t>广东省江门市江海区银帆路2号5幢(利生车城)</t>
         </is>
       </c>
     </row>
@@ -12480,7 +12480,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛凯德Mall</t>
+          <t>华为智能生活馆•青岛乐客城</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
+          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛乐客城</t>
+          <t>华为智能生活馆•青岛凯德Mall</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
+          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（南湖天地）</t>
+          <t>华为授权体验店（西田城）</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区南湖街道171号</t>
+          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
         </is>
       </c>
     </row>
@@ -12804,7 +12804,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（西田城）</t>
+          <t>华为授权体验店（南湖天地）</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
+          <t>浙江省嘉兴市南湖区南湖街道171号</t>
         </is>
       </c>
     </row>
@@ -13123,22 +13123,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13148,29 +13148,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13180,29 +13180,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13212,29 +13212,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
+          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13244,29 +13244,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
+          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13276,29 +13276,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
+          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
         </is>
       </c>
     </row>
@@ -13320,17 +13320,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13340,29 +13340,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
+          <t>广东省珠海市香洲区前山工业区华威路103号A-23号 → 广东省珠海市香洲区前山工业区华威路103号二手车车库103-A-23号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13372,7 +13372,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
+          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
         </is>
       </c>
     </row>
@@ -13384,17 +13384,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省珠海市香洲区前山工业区华威路103号A-23号 → 广东省珠海市香洲区前山工业区华威路103号二手车车库103-A-23号</t>
+          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
         </is>
       </c>
     </row>
@@ -13416,17 +13416,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13436,29 +13436,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
+          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13468,29 +13468,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13500,29 +13500,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13532,29 +13532,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13564,29 +13564,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13596,29 +13596,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13628,29 +13628,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13660,29 +13660,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13692,29 +13692,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
         </is>
       </c>
     </row>
@@ -13736,17 +13736,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13756,29 +13756,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13788,7 +13788,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
@@ -13800,17 +13800,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13820,7 +13820,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
@@ -13832,17 +13832,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13852,7 +13852,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
@@ -13864,17 +13864,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13884,29 +13884,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
+          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
         </is>
       </c>
     </row>
@@ -13933,12 +13933,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13948,29 +13948,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13980,29 +13980,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14012,29 +14012,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14044,29 +14044,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14076,29 +14076,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14108,7 +14108,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
@@ -14120,17 +14120,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14140,29 +14140,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
+          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
+          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
         </is>
       </c>
     </row>
@@ -14216,17 +14216,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14248,17 +14248,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14275,22 +14275,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14312,17 +14312,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14344,17 +14344,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14371,22 +14371,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14408,17 +14408,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14440,17 +14440,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14472,17 +14472,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14499,22 +14499,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14531,22 +14531,22 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14573,12 +14573,12 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14600,17 +14600,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14632,17 +14632,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14664,17 +14664,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14696,17 +14696,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14728,17 +14728,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14760,17 +14760,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14797,12 +14797,12 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14824,17 +14824,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14856,17 +14856,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14888,17 +14888,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14920,17 +14920,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14952,17 +14952,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14979,22 +14979,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15016,17 +15016,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15048,17 +15048,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15080,17 +15080,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15107,22 +15107,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15144,17 +15144,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15176,17 +15176,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15208,17 +15208,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15240,17 +15240,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15272,17 +15272,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15309,12 +15309,12 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15331,22 +15331,22 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15363,22 +15363,22 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15395,22 +15395,22 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15432,17 +15432,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -15459,22 +15459,22 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15496,17 +15496,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15523,22 +15523,22 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15560,17 +15560,17 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15592,17 +15592,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15624,17 +15624,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15656,17 +15656,17 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -15688,17 +15688,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15720,17 +15720,17 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15752,17 +15752,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15784,17 +15784,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15816,17 +15816,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15848,17 +15848,17 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15880,17 +15880,17 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15912,17 +15912,17 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15944,17 +15944,17 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15976,17 +15976,17 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16008,17 +16008,17 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16040,17 +16040,17 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16072,17 +16072,17 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -16109,12 +16109,12 @@
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16136,17 +16136,17 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16173,12 +16173,12 @@
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16200,17 +16200,17 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -16232,17 +16232,17 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16259,22 +16259,22 @@
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16296,17 +16296,17 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16328,17 +16328,17 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16355,22 +16355,22 @@
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16392,17 +16392,17 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16419,22 +16419,22 @@
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -16456,17 +16456,17 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16488,17 +16488,17 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16520,17 +16520,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16552,17 +16552,17 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16584,17 +16584,17 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16616,17 +16616,17 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16653,12 +16653,12 @@
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -16675,22 +16675,22 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16712,17 +16712,17 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16744,17 +16744,17 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -16771,22 +16771,22 @@
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16808,17 +16808,17 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16840,17 +16840,17 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -16872,17 +16872,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16904,17 +16904,17 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道服务中心</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16936,17 +16936,17 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16968,17 +16968,17 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -17000,17 +17000,17 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17032,17 +17032,17 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -17059,22 +17059,22 @@
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17096,17 +17096,17 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17128,17 +17128,17 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17160,17 +17160,17 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17187,22 +17187,22 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17219,22 +17219,22 @@
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17251,22 +17251,22 @@
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>牡丹江中信恒业</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>牡丹江中源恒业</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17288,17 +17288,17 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17320,17 +17320,17 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17352,17 +17352,17 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17384,17 +17384,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17416,17 +17416,17 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17448,17 +17448,17 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17480,17 +17480,17 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17512,17 +17512,17 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17539,22 +17539,22 @@
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -17576,17 +17576,17 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17608,17 +17608,17 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17640,17 +17640,17 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17672,17 +17672,17 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17699,22 +17699,22 @@
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17736,17 +17736,17 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17768,17 +17768,17 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17800,17 +17800,17 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17832,17 +17832,17 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17864,17 +17864,17 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17896,17 +17896,17 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17928,17 +17928,17 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17960,17 +17960,17 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -17992,17 +17992,17 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18019,22 +18019,22 @@
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18056,17 +18056,17 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18083,22 +18083,22 @@
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中信恒业</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中源恒业</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18120,17 +18120,17 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -18152,17 +18152,17 @@
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18184,17 +18184,17 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -18216,17 +18216,17 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18248,17 +18248,17 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -18280,17 +18280,17 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -18312,17 +18312,17 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -18344,17 +18344,17 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -18376,17 +18376,17 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -18408,17 +18408,17 @@
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -18435,22 +18435,22 @@
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -18472,17 +18472,17 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -18504,17 +18504,17 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -18536,17 +18536,17 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -18568,17 +18568,17 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
@@ -18627,22 +18627,22 @@
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
+          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
+          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
@@ -18652,29 +18652,29 @@
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 60%</t>
+          <t>地址相似度 88%</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•威海青岛南路</t>
+          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
+          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
@@ -18684,29 +18684,29 @@
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 69%</t>
+          <t>地址相似度 60%</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
+          <t>鸿蒙智行尚界用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
+          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
@@ -18716,29 +18716,29 @@
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 88%</t>
+          <t>地址相似度 69%</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>潍坊易豪4S中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>潍坊鑫易豪4S中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
@@ -18748,7 +18748,7 @@
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18760,17 +18760,17 @@
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
+          <t>小米汽车江西萍乡安源区萍乡天虹</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
+          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
@@ -18780,7 +18780,7 @@
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18792,17 +18792,17 @@
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
@@ -18812,7 +18812,7 @@
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18824,17 +18824,17 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路授权服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18856,17 +18856,17 @@
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
@@ -18876,7 +18876,7 @@
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18888,17 +18888,17 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西萍乡安源区萍乡天虹</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
@@ -18908,29 +18908,29 @@
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
+          <t>潍坊易豪4S中心</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
+          <t>潍坊鑫易豪4S中心</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
@@ -18940,7 +18940,7 @@
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
@@ -18952,17 +18952,17 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
+          <t>小米汽车兴义市桔康路授权服务中心</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
+          <t>小米汽车兴义市桔康路服务中心</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
@@ -18972,7 +18972,7 @@
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 91%</t>
         </is>
       </c>
     </row>
@@ -18984,17 +18984,17 @@
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路授权服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 91%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -19016,17 +19016,17 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
@@ -19048,17 +19048,17 @@
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
+          <t>小米汽车天津西青区卫津南路授权服务中心</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
+          <t>小米汽车天津西青区卫津南路服务中心</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -10542,7 +10542,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春中东新天地零售中心</t>
+          <t>理想汽车长春华润万象城零售中心</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区亚泰大街1138号</t>
+          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
         </is>
       </c>
     </row>
@@ -10569,7 +10569,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春华润万象城零售中心</t>
+          <t>理想汽车长春中东新天地零售中心</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
+          <t>吉林省长春市南关区亚泰大街1138号</t>
         </is>
       </c>
     </row>
@@ -10893,7 +10893,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南西城龙湖天街广场</t>
+          <t>蔚来空间 | 济南世纪大道万达广场</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
+          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
         </is>
       </c>
     </row>
@@ -10920,7 +10920,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南世纪大道万达广场</t>
+          <t>蔚来空间 | 济南西城龙湖天街广场</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
+          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京龙湖长楹天街</t>
+          <t>鸿蒙智行智界用户中心•北京房山城关</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通路1号院龙湖长楹天街东区一层B栋-2F-C32，B栋-1F-19a，B栋-2F-21，B栋-1F-19b，B栋-2F-19a，B栋-2F-19b，B栋-2F-20号商铺</t>
+          <t>北京市房山区城关街道顾八路一区2号</t>
         </is>
       </c>
     </row>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•北京房山城关</t>
+          <t>华为智能生活馆•北京龙湖长楹天街</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>北京市房山区城关街道顾八路一区2号</t>
+          <t>北京市朝阳区常通路1号院龙湖长楹天街东区一层B栋-2F-C32，B栋-1F-19a，B栋-2F-21，B栋-1F-19b，B栋-2F-19a，B栋-2F-19b，B栋-2F-20号商铺</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
+          <t>AITO授权用户中心•宁波下应</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•宁波下应</t>
+          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>理想汽车江门江海零售中心</t>
+          <t>理想汽车江门江海服务中心（利生车城店）</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>江门市江海区银帆路2号5幢-2</t>
+          <t>广东省江门市江海区银帆路2号5幢(利生车城)</t>
         </is>
       </c>
     </row>
@@ -11805,7 +11805,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>理想汽车江门江海服务中心（利生车城店）</t>
+          <t>理想汽车江门江海零售中心</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>广东省江门市江海区银帆路2号5幢(利生车城)</t>
+          <t>江门市江海区银帆路2号5幢-2</t>
         </is>
       </c>
     </row>
@@ -12075,7 +12075,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-福田电气化体验馆</t>
+          <t>深圳中升悦晟-罗湖卫星展厅</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
+          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
         </is>
       </c>
     </row>
@@ -12102,7 +12102,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-罗湖卫星展厅</t>
+          <t>深圳中升悦晟-福田电气化体验馆</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
+          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
         </is>
       </c>
     </row>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（长楹龙湖）</t>
+          <t>鸿蒙智行授权用户中心•北京王四营</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
+          <t>北京市朝阳区王四营339号</t>
         </is>
       </c>
     </row>
@@ -12210,7 +12210,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京王四营</t>
+          <t>华为授权体验店（长楹龙湖）</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营339号</t>
+          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
         </is>
       </c>
     </row>
@@ -12480,7 +12480,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛乐客城</t>
+          <t>华为智能生活馆•青岛凯德Mall</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
+          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛凯德Mall</t>
+          <t>华为智能生活馆•青岛乐客城</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
+          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（西田城）</t>
+          <t>华为授权体验店（星河COCOCity）</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
+          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（星河COCOCity）</t>
+          <t>华为授权体验店（西田城）</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
+          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
         </is>
       </c>
     </row>
@@ -13123,22 +13123,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13148,29 +13148,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
+          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
+          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
         </is>
       </c>
     </row>
@@ -13192,17 +13192,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13212,29 +13212,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
+          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13244,29 +13244,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
+          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13276,29 +13276,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13308,29 +13308,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13340,29 +13340,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省珠海市香洲区前山工业区华威路103号A-23号 → 广东省珠海市香洲区前山工业区华威路103号二手车车库103-A-23号</t>
+          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13372,7 +13372,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
+          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
         </is>
       </c>
     </row>
@@ -13384,17 +13384,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13404,29 +13404,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13436,29 +13436,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13468,29 +13468,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13500,29 +13500,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13532,29 +13532,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13564,29 +13564,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13596,29 +13596,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
         </is>
       </c>
     </row>
@@ -13640,17 +13640,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13660,29 +13660,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13692,29 +13692,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
+          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13724,29 +13724,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
+          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13756,29 +13756,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13788,7 +13788,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
         </is>
       </c>
     </row>
@@ -13800,17 +13800,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13820,29 +13820,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13852,29 +13852,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13884,29 +13884,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13916,29 +13916,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
+          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
         </is>
       </c>
     </row>
@@ -13960,17 +13960,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
@@ -14019,22 +14019,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14044,7 +14044,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
         </is>
       </c>
     </row>
@@ -14056,17 +14056,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
@@ -14088,17 +14088,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14108,29 +14108,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>广东省珠海市香洲区前山工业区华威路103号A-23号 → 广东省珠海市香洲区前山工业区华威路103号二手车车库103-A-23号</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14140,29 +14140,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
@@ -14216,17 +14216,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14248,17 +14248,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14275,22 +14275,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14344,17 +14344,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14371,22 +14371,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14408,17 +14408,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14440,17 +14440,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14472,17 +14472,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14499,22 +14499,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14536,17 +14536,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14573,12 +14573,12 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14600,17 +14600,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14632,17 +14632,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14664,17 +14664,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14696,17 +14696,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14723,22 +14723,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14760,17 +14760,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14792,17 +14792,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14824,17 +14824,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14856,17 +14856,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14883,22 +14883,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14920,17 +14920,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14952,17 +14952,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14984,17 +14984,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15021,12 +15021,12 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15048,17 +15048,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15080,17 +15080,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15107,22 +15107,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15144,17 +15144,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15181,12 +15181,12 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15208,17 +15208,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15240,17 +15240,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15272,17 +15272,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15304,17 +15304,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15331,22 +15331,22 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15363,7 +15363,7 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -15373,12 +15373,12 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15400,17 +15400,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15464,17 +15464,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15496,17 +15496,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15523,22 +15523,22 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15555,22 +15555,22 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15592,17 +15592,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15624,17 +15624,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15683,22 +15683,22 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15720,17 +15720,17 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15752,17 +15752,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15789,12 +15789,12 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15816,17 +15816,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15848,17 +15848,17 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15880,17 +15880,17 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15912,17 +15912,17 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15944,17 +15944,17 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15976,17 +15976,17 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16008,17 +16008,17 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16040,17 +16040,17 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16072,17 +16072,17 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -16104,17 +16104,17 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16136,17 +16136,17 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16168,17 +16168,17 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16200,17 +16200,17 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -16232,17 +16232,17 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16259,22 +16259,22 @@
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16291,22 +16291,22 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>牡丹江中信恒业</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>牡丹江中源恒业</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16328,17 +16328,17 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16355,7 +16355,7 @@
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
@@ -16365,12 +16365,12 @@
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16392,17 +16392,17 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16424,17 +16424,17 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -16451,22 +16451,22 @@
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16488,17 +16488,17 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16520,17 +16520,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16552,17 +16552,17 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16584,17 +16584,17 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16616,17 +16616,17 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16648,17 +16648,17 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -16675,22 +16675,22 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16712,17 +16712,17 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16744,17 +16744,17 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -16776,17 +16776,17 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16808,17 +16808,17 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16835,22 +16835,22 @@
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -16872,17 +16872,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16904,17 +16904,17 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16941,12 +16941,12 @@
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16968,17 +16968,17 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -17000,17 +17000,17 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17032,17 +17032,17 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -17059,22 +17059,22 @@
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17091,22 +17091,22 @@
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17128,17 +17128,17 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17155,22 +17155,22 @@
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17187,22 +17187,22 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小米汽车广东河源市源城区河源大道服务中心</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17224,17 +17224,17 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17251,22 +17251,22 @@
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中信恒业</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中源恒业</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17320,17 +17320,17 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17352,17 +17352,17 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17384,17 +17384,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17416,17 +17416,17 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17448,17 +17448,17 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17480,17 +17480,17 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17512,17 +17512,17 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17544,17 +17544,17 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -17576,17 +17576,17 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17608,17 +17608,17 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17640,17 +17640,17 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17672,17 +17672,17 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17704,17 +17704,17 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17736,17 +17736,17 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17768,17 +17768,17 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17800,17 +17800,17 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17827,22 +17827,22 @@
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17864,17 +17864,17 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17896,17 +17896,17 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17928,17 +17928,17 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17965,12 +17965,12 @@
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -17987,22 +17987,22 @@
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18019,22 +18019,22 @@
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18056,17 +18056,17 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18088,17 +18088,17 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18120,17 +18120,17 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -18152,17 +18152,17 @@
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18184,17 +18184,17 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -18216,17 +18216,17 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18248,17 +18248,17 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -18280,17 +18280,17 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -18312,17 +18312,17 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -18344,17 +18344,17 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -18371,22 +18371,22 @@
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -18408,17 +18408,17 @@
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -18440,17 +18440,17 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -18477,12 +18477,12 @@
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -18504,17 +18504,17 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -18536,17 +18536,17 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -18568,17 +18568,17 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
@@ -18605,12 +18605,12 @@
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
+          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
+          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
@@ -18637,12 +18637,12 @@
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
@@ -18659,22 +18659,22 @@
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
+          <t>鸿蒙智行尚界用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
+          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
@@ -18684,29 +18684,29 @@
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 60%</t>
+          <t>地址相似度 69%</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•威海青岛南路</t>
+          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
+          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 69%</t>
+          <t>地址相似度 60%</t>
         </is>
       </c>
     </row>
@@ -18733,12 +18733,12 @@
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>小米汽车江西萍乡安源区萍乡天虹</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
@@ -18748,7 +18748,7 @@
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18760,17 +18760,17 @@
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西萍乡安源区萍乡天虹</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
@@ -18780,29 +18780,29 @@
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
+          <t>潍坊易豪4S中心</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
+          <t>潍坊鑫易豪4S中心</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
@@ -18812,7 +18812,7 @@
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
@@ -18824,17 +18824,17 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
+          <t>小米汽车兴义市桔康路授权服务中心</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
+          <t>小米汽车兴义市桔康路服务中心</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 91%</t>
         </is>
       </c>
     </row>
@@ -18856,17 +18856,17 @@
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
@@ -18876,7 +18876,7 @@
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18888,17 +18888,17 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
@@ -18908,29 +18908,29 @@
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>潍坊易豪4S中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>潍坊鑫易豪4S中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
@@ -18940,7 +18940,7 @@
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18952,17 +18952,17 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路授权服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
@@ -18972,7 +18972,7 @@
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 91%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18984,17 +18984,17 @@
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -19016,17 +19016,17 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
@@ -19036,7 +19036,7 @@
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -10542,7 +10542,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春华润万象城零售中心</t>
+          <t>理想汽车长春中东新天地零售中心</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
+          <t>吉林省长春市南关区亚泰大街1138号</t>
         </is>
       </c>
     </row>
@@ -10569,7 +10569,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春中东新天地零售中心</t>
+          <t>理想汽车长春华润万象城零售中心</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区亚泰大街1138号</t>
+          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•北京房山城关</t>
+          <t>华为智能生活馆•北京龙湖长楹天街</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>北京市房山区城关街道顾八路一区2号</t>
+          <t>北京市朝阳区常通路1号院龙湖长楹天街东区一层B栋-2F-C32，B栋-1F-19a，B栋-2F-21，B栋-1F-19b，B栋-2F-19a，B栋-2F-19b，B栋-2F-20号商铺</t>
         </is>
       </c>
     </row>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京龙湖长楹天街</t>
+          <t>鸿蒙智行智界用户中心•北京房山城关</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通路1号院龙湖长楹天街东区一层B栋-2F-C32，B栋-1F-19a，B栋-2F-21，B栋-1F-19b，B栋-2F-19a，B栋-2F-19b，B栋-2F-20号商铺</t>
+          <t>北京市房山区城关街道顾八路一区2号</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•成都惠王陵西路</t>
+          <t>鸿蒙智行智界用户中心•成都武侯大道</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市龙泉驿区惠王陵西路155号</t>
+          <t>四川省成都市武侯区武侯大道顺江段61号</t>
         </is>
       </c>
     </row>
@@ -11055,7 +11055,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•成都武侯大道</t>
+          <t>鸿蒙智行尚界用户中心•成都惠王陵西路</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市武侯区武侯大道顺江段61号</t>
+          <t>四川省成都市龙泉驿区惠王陵西路155号</t>
         </is>
       </c>
     </row>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>理想汽车江门江海服务中心（利生车城店）</t>
+          <t>理想汽车江门江海零售中心</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>广东省江门市江海区银帆路2号5幢(利生车城)</t>
+          <t>江门市江海区银帆路2号5幢-2</t>
         </is>
       </c>
     </row>
@@ -11805,7 +11805,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>理想汽车江门江海零售中心</t>
+          <t>理想汽车江门江海服务中心（利生车城店）</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>江门市江海区银帆路2号5幢-2</t>
+          <t>广东省江门市江海区银帆路2号5幢(利生车城)</t>
         </is>
       </c>
     </row>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>理想汽车衢州吾悦广场零售中心</t>
+          <t>理想汽车衢州衢江服务中心（振兴东路店）</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区白云中大道路99号吾悦广场1019-1商铺理想汽车</t>
+          <t>衢州市衢江区振兴东路599号</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江服务中心（振兴东路店）</t>
+          <t>理想汽车衢州吾悦广场零售中心</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>衢州市衢江区振兴东路599号</t>
+          <t>浙江省衢州市柯城区白云中大道路99号吾悦广场1019-1商铺理想汽车</t>
         </is>
       </c>
     </row>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京王四营</t>
+          <t>华为授权体验店（长楹龙湖）</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营339号</t>
+          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
         </is>
       </c>
     </row>
@@ -12210,7 +12210,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（长楹龙湖）</t>
+          <t>华为智能生活馆•北京颐堤港</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
+          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
         </is>
       </c>
     </row>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京颐堤港</t>
+          <t>鸿蒙智行授权用户中心•北京王四营</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
+          <t>北京市朝阳区王四营339号</t>
         </is>
       </c>
     </row>
@@ -12480,7 +12480,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛凯德Mall</t>
+          <t>华为智能生活馆•青岛乐客城</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
+          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛乐客城</t>
+          <t>华为智能生活馆•青岛凯德Mall</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
+          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
         </is>
       </c>
     </row>
@@ -13123,22 +13123,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13148,29 +13148,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
         </is>
       </c>
     </row>
@@ -13192,17 +13192,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13212,29 +13212,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
@@ -13256,17 +13256,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13276,29 +13276,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
+          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13308,29 +13308,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13340,7 +13340,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
         </is>
       </c>
     </row>
@@ -13352,17 +13352,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13372,7 +13372,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
+          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
         </is>
       </c>
     </row>
@@ -13384,17 +13384,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13404,29 +13404,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
+          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
         </is>
       </c>
     </row>
@@ -13475,22 +13475,22 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13500,7 +13500,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
+          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
         </is>
       </c>
     </row>
@@ -13512,17 +13512,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13532,7 +13532,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
@@ -13544,17 +13544,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13564,14 +13564,14 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -13581,12 +13581,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13596,29 +13596,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13628,29 +13628,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
+          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
         </is>
       </c>
     </row>
@@ -13672,17 +13672,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13692,29 +13692,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13724,29 +13724,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
+          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13756,29 +13756,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13788,7 +13788,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
+          <t>广东省珠海市香洲区前山工业区华威路103号A-23号 → 广东省珠海市香洲区前山工业区华威路103号二手车车库103-A-23号</t>
         </is>
       </c>
     </row>
@@ -13800,17 +13800,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13820,29 +13820,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
+          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13852,29 +13852,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13884,29 +13884,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13916,29 +13916,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
+          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
         </is>
       </c>
     </row>
@@ -13960,17 +13960,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13980,29 +13980,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14012,29 +14012,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14044,29 +14044,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14076,29 +14076,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14108,29 +14108,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>广东省珠海市香洲区前山工业区华威路103号A-23号 → 广东省珠海市香洲区前山工业区华威路103号二手车车库103-A-23号</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14140,29 +14140,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
         </is>
       </c>
     </row>
@@ -14216,17 +14216,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14243,22 +14243,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14285,12 +14285,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14312,17 +14312,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14344,17 +14344,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14376,17 +14376,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14408,17 +14408,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14440,17 +14440,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14472,17 +14472,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14499,7 +14499,7 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -14509,12 +14509,12 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14536,17 +14536,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14568,17 +14568,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14600,17 +14600,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14632,17 +14632,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14664,17 +14664,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14696,17 +14696,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14723,22 +14723,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14760,17 +14760,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14792,17 +14792,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14819,22 +14819,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14856,17 +14856,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14883,7 +14883,7 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -14893,12 +14893,12 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14915,7 +14915,7 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14952,17 +14952,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14984,17 +14984,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15016,17 +15016,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15048,17 +15048,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15080,17 +15080,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15112,17 +15112,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15139,22 +15139,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15171,22 +15171,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15208,17 +15208,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15240,17 +15240,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道服务中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15272,17 +15272,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15304,17 +15304,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15368,17 +15368,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15395,22 +15395,22 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15432,17 +15432,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -15464,17 +15464,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15496,17 +15496,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15528,17 +15528,17 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15555,22 +15555,22 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15597,12 +15597,12 @@
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15624,17 +15624,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15656,17 +15656,17 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -15683,22 +15683,22 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15720,17 +15720,17 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15752,17 +15752,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15784,17 +15784,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15816,17 +15816,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15880,17 +15880,17 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15912,17 +15912,17 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15944,17 +15944,17 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15976,17 +15976,17 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16003,22 +16003,22 @@
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16040,17 +16040,17 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16072,17 +16072,17 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -16099,22 +16099,22 @@
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>牡丹江中信恒业</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>牡丹江中源恒业</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16136,17 +16136,17 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16168,17 +16168,17 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16200,17 +16200,17 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -16232,17 +16232,17 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16264,17 +16264,17 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16291,22 +16291,22 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中信恒业</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中源恒业</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16328,17 +16328,17 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16360,17 +16360,17 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16392,17 +16392,17 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16424,17 +16424,17 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -16451,22 +16451,22 @@
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16488,17 +16488,17 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16520,17 +16520,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16552,17 +16552,17 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16584,17 +16584,17 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16616,17 +16616,17 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16648,17 +16648,17 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -16685,12 +16685,12 @@
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16712,17 +16712,17 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16739,22 +16739,22 @@
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -16776,17 +16776,17 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16808,17 +16808,17 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16835,22 +16835,22 @@
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -16872,17 +16872,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16904,17 +16904,17 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16936,17 +16936,17 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16968,17 +16968,17 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -17000,17 +17000,17 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17032,17 +17032,17 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -17069,12 +17069,12 @@
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17091,22 +17091,22 @@
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17128,17 +17128,17 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17155,7 +17155,7 @@
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
@@ -17165,12 +17165,12 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17192,17 +17192,17 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17224,17 +17224,17 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17256,17 +17256,17 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17288,17 +17288,17 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17325,12 +17325,12 @@
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17352,17 +17352,17 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17384,17 +17384,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17416,17 +17416,17 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17443,22 +17443,22 @@
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17480,17 +17480,17 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17512,17 +17512,17 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17544,17 +17544,17 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -17576,17 +17576,17 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17608,17 +17608,17 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17635,7 +17635,7 @@
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
@@ -17645,12 +17645,12 @@
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17672,17 +17672,17 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17704,17 +17704,17 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17736,17 +17736,17 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17768,17 +17768,17 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17800,17 +17800,17 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17827,22 +17827,22 @@
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17864,17 +17864,17 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17896,17 +17896,17 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17928,17 +17928,17 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17960,17 +17960,17 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -17992,17 +17992,17 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18024,17 +18024,17 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18056,17 +18056,17 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18088,17 +18088,17 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18120,17 +18120,17 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -18152,17 +18152,17 @@
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18179,22 +18179,22 @@
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -18216,17 +18216,17 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18248,17 +18248,17 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -18280,17 +18280,17 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -18312,17 +18312,17 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -18344,17 +18344,17 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -18371,22 +18371,22 @@
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -18408,17 +18408,17 @@
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -18440,17 +18440,17 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -18472,17 +18472,17 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -18504,17 +18504,17 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -18536,17 +18536,17 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -18568,17 +18568,17 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
@@ -18595,22 +18595,22 @@
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
+          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
+          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
@@ -18620,7 +18620,7 @@
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 88%</t>
+          <t>地址相似度 60%</t>
         </is>
       </c>
     </row>
@@ -18691,22 +18691,22 @@
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
+          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
+          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 60%</t>
+          <t>地址相似度 88%</t>
         </is>
       </c>
     </row>
@@ -18728,17 +18728,17 @@
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西萍乡安源区萍乡天虹</t>
+          <t>小米汽车兴义市桔康路授权服务中心</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
+          <t>小米汽车兴义市桔康路服务中心</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
@@ -18748,29 +18748,29 @@
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 91%</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
+          <t>潍坊易豪4S中心</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
+          <t>潍坊鑫易豪4S中心</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
@@ -18780,29 +18780,29 @@
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>潍坊易豪4S中心</t>
+          <t>小米汽车天津西青区卫津南路授权服务中心</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>潍坊鑫易豪4S中心</t>
+          <t>小米汽车天津西青区卫津南路服务中心</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
@@ -18812,7 +18812,7 @@
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18824,17 +18824,17 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路授权服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 91%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18856,17 +18856,17 @@
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
@@ -18876,7 +18876,7 @@
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18888,17 +18888,17 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
@@ -18908,7 +18908,7 @@
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18920,17 +18920,17 @@
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
@@ -18940,7 +18940,7 @@
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18952,17 +18952,17 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
+          <t>小米汽车江西萍乡安源区萍乡天虹</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
+          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
@@ -18972,7 +18972,7 @@
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18984,17 +18984,17 @@
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -19048,17 +19048,17 @@
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路授权服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -10083,7 +10083,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区西四环双林东路服务中心</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>双林东路8号万开基地二期B座</t>
+          <t>北京市大兴区大兴龙湖天街一层中庭</t>
         </is>
       </c>
     </row>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京丰台区西四环双林东路服务中心</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>北京市大兴区大兴龙湖天街一层中庭</t>
+          <t>双林东路8号万开基地二期B座</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>小米汽车安徽省合肥市庐阳区万象汇</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>东塘路80号合肥巢湖万达广场1F</t>
+          <t>安徽省合肥市庐阳区庐阳万象汇1F1号门入口</t>
         </is>
       </c>
     </row>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市庐阳区万象汇</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>安徽省合肥市庐阳区庐阳万象汇1F1号门入口</t>
+          <t>东塘路80号合肥巢湖万达广场1F</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区永川万达</t>
+          <t>小米汽车重庆市江津区爱情海购物广场</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>中国重庆市永川区星光大道789号永川万达</t>
+          <t>重庆市江津区爱情海购物广场L1层中庭</t>
         </is>
       </c>
     </row>
@@ -10353,7 +10353,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市江津区爱情海购物广场</t>
+          <t>小米汽车重庆市永川区永川万达</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>重庆市江津区爱情海购物广场L1层中庭</t>
+          <t>中国重庆市永川区星光大道789号永川万达</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•成都武侯大道</t>
+          <t>鸿蒙智行尚界用户中心•成都惠王陵西路</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市武侯区武侯大道顺江段61号</t>
+          <t>四川省成都市龙泉驿区惠王陵西路155号</t>
         </is>
       </c>
     </row>
@@ -11055,7 +11055,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•成都惠王陵西路</t>
+          <t>鸿蒙智行智界用户中心•成都武侯大道</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市龙泉驿区惠王陵西路155号</t>
+          <t>四川省成都市武侯区武侯大道顺江段61号</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•宁波下应</t>
+          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
+          <t>AITO授权用户中心•宁波下应</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江服务中心（振兴东路店）</t>
+          <t>理想汽车衢州吾悦广场零售中心</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>衢州市衢江区振兴东路599号</t>
+          <t>浙江省衢州市柯城区白云中大道路99号吾悦广场1019-1商铺理想汽车</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>理想汽车衢州吾悦广场零售中心</t>
+          <t>理想汽车衢州衢江服务中心（振兴东路店）</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区白云中大道路99号吾悦广场1019-1商铺理想汽车</t>
+          <t>衢州市衢江区振兴东路599号</t>
         </is>
       </c>
     </row>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（长楹龙湖）</t>
+          <t>华为智能生活馆•北京颐堤港</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
+          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
         </is>
       </c>
     </row>
@@ -12210,7 +12210,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京颐堤港</t>
+          <t>鸿蒙智行授权用户中心•北京王四营</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
+          <t>北京市朝阳区王四营339号</t>
         </is>
       </c>
     </row>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京王四营</t>
+          <t>华为授权体验店（长楹龙湖）</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营339号</t>
+          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
         </is>
       </c>
     </row>
@@ -12480,7 +12480,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛乐客城</t>
+          <t>华为智能生活馆•青岛凯德Mall</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
+          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛凯德Mall</t>
+          <t>华为智能生活馆•青岛乐客城</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
+          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（星河COCOCity）</t>
+          <t>华为授权体验店（西田城）</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
+          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（西田城）</t>
+          <t>华为授权体验店（星河COCOCity）</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
+          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
         </is>
       </c>
     </row>
@@ -13123,22 +13123,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13148,29 +13148,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13180,29 +13180,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13212,7 +13212,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
@@ -13224,17 +13224,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
@@ -13256,17 +13256,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13276,29 +13276,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
+          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
         </is>
       </c>
     </row>
@@ -13320,17 +13320,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13340,7 +13340,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
+          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
         </is>
       </c>
     </row>
@@ -13352,17 +13352,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13372,7 +13372,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
@@ -13384,17 +13384,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13404,29 +13404,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13436,29 +13436,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
+          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13468,14 +13468,14 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13500,29 +13500,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13532,7 +13532,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
         </is>
       </c>
     </row>
@@ -13544,17 +13544,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13564,14 +13564,14 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -13581,12 +13581,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13596,29 +13596,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13628,29 +13628,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
+          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13660,29 +13660,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
+          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13692,29 +13692,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13724,29 +13724,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
         </is>
       </c>
     </row>
@@ -13768,17 +13768,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13788,29 +13788,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>广东省珠海市香洲区前山工业区华威路103号A-23号 → 广东省珠海市香洲区前山工业区华威路103号二手车车库103-A-23号</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13820,7 +13820,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
+          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
         </is>
       </c>
     </row>
@@ -13832,17 +13832,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13852,29 +13852,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>广东省珠海市香洲区前山工业区华威路103号A-23号 → 广东省珠海市香洲区前山工业区华威路103号二手车车库103-A-23号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13884,29 +13884,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13916,29 +13916,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
+          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
@@ -13960,17 +13960,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13980,29 +13980,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14012,29 +14012,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14044,29 +14044,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14076,29 +14076,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
+          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14108,29 +14108,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14140,29 +14140,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
+          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
         </is>
       </c>
     </row>
@@ -14216,17 +14216,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14243,22 +14243,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14280,17 +14280,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14312,17 +14312,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14339,22 +14339,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14376,17 +14376,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14408,17 +14408,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14440,17 +14440,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14472,17 +14472,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14504,17 +14504,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14536,17 +14536,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14573,12 +14573,12 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14600,17 +14600,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14632,17 +14632,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14664,17 +14664,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14696,17 +14696,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14728,17 +14728,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14760,17 +14760,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14792,17 +14792,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14819,22 +14819,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14856,17 +14856,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14888,17 +14888,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14915,22 +14915,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14952,17 +14952,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道服务中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14984,17 +14984,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15016,17 +15016,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15048,17 +15048,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15080,17 +15080,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15112,17 +15112,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15139,22 +15139,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15171,7 +15171,7 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -15181,12 +15181,12 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15208,17 +15208,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15240,17 +15240,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15272,17 +15272,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15304,17 +15304,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15331,22 +15331,22 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15363,22 +15363,22 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15395,22 +15395,22 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15432,17 +15432,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -15464,17 +15464,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15496,17 +15496,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15528,17 +15528,17 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15555,22 +15555,22 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15592,17 +15592,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15624,17 +15624,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15656,17 +15656,17 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -15688,17 +15688,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15720,17 +15720,17 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15752,17 +15752,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15784,17 +15784,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15816,17 +15816,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15848,17 +15848,17 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15880,17 +15880,17 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15912,17 +15912,17 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15944,17 +15944,17 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15971,22 +15971,22 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16003,22 +16003,22 @@
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16040,17 +16040,17 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16072,17 +16072,17 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -16099,22 +16099,22 @@
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中信恒业</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中源恒业</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16136,17 +16136,17 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16168,17 +16168,17 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16195,22 +16195,22 @@
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -16232,17 +16232,17 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16264,17 +16264,17 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16296,17 +16296,17 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16328,17 +16328,17 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16360,17 +16360,17 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16387,22 +16387,22 @@
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16429,12 +16429,12 @@
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -16456,17 +16456,17 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16488,17 +16488,17 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16520,17 +16520,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16552,17 +16552,17 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16584,17 +16584,17 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16616,17 +16616,17 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16648,17 +16648,17 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -16675,22 +16675,22 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>牡丹江中信恒业</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>牡丹江中源恒业</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16707,22 +16707,22 @@
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16739,22 +16739,22 @@
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -16776,17 +16776,17 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16808,17 +16808,17 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16840,17 +16840,17 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -16872,17 +16872,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16904,17 +16904,17 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16936,17 +16936,17 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16968,17 +16968,17 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -17000,17 +17000,17 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17032,17 +17032,17 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -17064,17 +17064,17 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17096,17 +17096,17 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17128,17 +17128,17 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17160,17 +17160,17 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17192,17 +17192,17 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17224,17 +17224,17 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17256,17 +17256,17 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17288,17 +17288,17 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17320,17 +17320,17 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17352,17 +17352,17 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17384,17 +17384,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17416,17 +17416,17 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17443,22 +17443,22 @@
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17480,17 +17480,17 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17512,17 +17512,17 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17544,17 +17544,17 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -17576,17 +17576,17 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17603,22 +17603,22 @@
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17635,22 +17635,22 @@
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17672,17 +17672,17 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17704,17 +17704,17 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17736,17 +17736,17 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17768,17 +17768,17 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17800,17 +17800,17 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17832,17 +17832,17 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17864,17 +17864,17 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17896,17 +17896,17 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17928,17 +17928,17 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17960,17 +17960,17 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -17987,22 +17987,22 @@
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18024,17 +18024,17 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18051,22 +18051,22 @@
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18088,17 +18088,17 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18120,17 +18120,17 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -18152,17 +18152,17 @@
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18179,22 +18179,22 @@
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -18216,17 +18216,17 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18248,17 +18248,17 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -18280,17 +18280,17 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -18312,17 +18312,17 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -18344,17 +18344,17 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -18376,17 +18376,17 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -18408,17 +18408,17 @@
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -18440,17 +18440,17 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -18472,17 +18472,17 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -18504,17 +18504,17 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -18536,17 +18536,17 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -18568,17 +18568,17 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
@@ -18595,22 +18595,22 @@
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
+          <t>鸿蒙智行尚界用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
+          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
@@ -18620,29 +18620,29 @@
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 60%</t>
+          <t>地址相似度 69%</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
+          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
+          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
@@ -18652,29 +18652,29 @@
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 88%</t>
+          <t>地址相似度 60%</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•威海青岛南路</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
@@ -18684,7 +18684,7 @@
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 69%</t>
+          <t>地址相似度 88%</t>
         </is>
       </c>
     </row>
@@ -18728,17 +18728,17 @@
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路授权服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
@@ -18748,29 +18748,29 @@
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 91%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>潍坊易豪4S中心</t>
+          <t>小米汽车天津西青区卫津南路授权服务中心</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>潍坊鑫易豪4S中心</t>
+          <t>小米汽车天津西青区卫津南路服务中心</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
@@ -18780,7 +18780,7 @@
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18792,17 +18792,17 @@
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路授权服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
@@ -18812,7 +18812,7 @@
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18824,17 +18824,17 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
@@ -18856,17 +18856,17 @@
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
+          <t>小米汽车江西萍乡安源区萍乡天虹</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
+          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
@@ -18876,7 +18876,7 @@
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18888,17 +18888,17 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>小米汽车兴义市桔康路授权服务中心</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>小米汽车兴义市桔康路服务中心</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
@@ -18908,7 +18908,7 @@
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 91%</t>
         </is>
       </c>
     </row>
@@ -18920,17 +18920,17 @@
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
@@ -18940,7 +18940,7 @@
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18952,17 +18952,17 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西萍乡安源区萍乡天虹</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
@@ -18972,7 +18972,7 @@
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -19016,17 +19016,17 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
@@ -19036,29 +19036,29 @@
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
+          <t>潍坊易豪4S中心</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
+          <t>潍坊鑫易豪4S中心</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -10083,7 +10083,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京丰台区西四环双林东路服务中心</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>北京市大兴区大兴龙湖天街一层中庭</t>
+          <t>双林东路8号万开基地二期B座</t>
         </is>
       </c>
     </row>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区西四环双林东路服务中心</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>双林东路8号万开基地二期B座</t>
+          <t>北京市大兴区大兴龙湖天街一层中庭</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市庐阳区万象汇</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>安徽省合肥市庐阳区庐阳万象汇1F1号门入口</t>
+          <t>东塘路80号合肥巢湖万达广场1F</t>
         </is>
       </c>
     </row>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>小米汽车安徽省合肥市庐阳区万象汇</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>东塘路80号合肥巢湖万达广场1F</t>
+          <t>安徽省合肥市庐阳区庐阳万象汇1F1号门入口</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春中东新天地零售中心</t>
+          <t>理想汽车长春华润万象城零售中心</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区亚泰大街1138号</t>
+          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
         </is>
       </c>
     </row>
@@ -10569,7 +10569,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春华润万象城零售中心</t>
+          <t>理想汽车长春中东新天地零售中心</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
+          <t>吉林省长春市南关区亚泰大街1138号</t>
         </is>
       </c>
     </row>
@@ -12480,7 +12480,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛凯德Mall</t>
+          <t>华为智能生活馆•青岛乐客城</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
+          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛乐客城</t>
+          <t>华为智能生活馆•青岛凯德Mall</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
+          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（西田城）</t>
+          <t>华为授权体验店（星河COCOCity）</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
+          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（星河COCOCity）</t>
+          <t>华为授权体验店（西田城）</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
+          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
         </is>
       </c>
     </row>
@@ -13123,22 +13123,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13148,29 +13148,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13180,29 +13180,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13212,29 +13212,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
@@ -13256,17 +13256,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13276,29 +13276,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13308,29 +13308,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
+          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13340,29 +13340,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13372,29 +13372,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
         </is>
       </c>
     </row>
@@ -13416,17 +13416,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13436,29 +13436,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
+          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13468,29 +13468,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13500,29 +13500,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13532,29 +13532,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13564,7 +13564,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
@@ -13603,22 +13603,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13628,29 +13628,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
+          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13660,29 +13660,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
+          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13692,7 +13692,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
+          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
         </is>
       </c>
     </row>
@@ -13704,17 +13704,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13724,29 +13724,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13756,29 +13756,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
+          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13788,29 +13788,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13820,29 +13820,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13852,29 +13852,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>广东省珠海市香洲区前山工业区华威路103号A-23号 → 广东省珠海市香洲区前山工业区华威路103号二手车车库103-A-23号</t>
+          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
@@ -13896,17 +13896,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
+          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
         </is>
       </c>
     </row>
@@ -13928,17 +13928,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13948,29 +13948,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13980,29 +13980,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14012,7 +14012,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
+          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
         </is>
       </c>
     </row>
@@ -14024,17 +14024,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14044,29 +14044,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
+          <t>广东省珠海市香洲区前山工业区华威路103号A-23号 → 广东省珠海市香洲区前山工业区华威路103号二手车车库103-A-23号</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14076,29 +14076,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
+          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14108,29 +14108,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14140,14 +14140,14 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -14157,12 +14157,12 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
@@ -14216,17 +14216,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14243,22 +14243,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14280,17 +14280,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14312,17 +14312,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14339,22 +14339,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14376,17 +14376,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14408,17 +14408,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14440,17 +14440,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14472,17 +14472,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14504,17 +14504,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14536,17 +14536,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14568,17 +14568,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14600,17 +14600,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14632,17 +14632,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14664,17 +14664,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14691,22 +14691,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14728,17 +14728,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14755,22 +14755,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14792,17 +14792,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14824,17 +14824,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14856,17 +14856,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14888,17 +14888,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14920,17 +14920,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14952,17 +14952,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14979,22 +14979,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15016,17 +15016,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15048,17 +15048,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15080,17 +15080,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15112,17 +15112,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15144,17 +15144,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15176,17 +15176,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15208,17 +15208,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15240,17 +15240,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15272,17 +15272,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15304,17 +15304,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15331,22 +15331,22 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15363,22 +15363,22 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15400,17 +15400,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15432,17 +15432,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -15459,22 +15459,22 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15501,12 +15501,12 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15523,22 +15523,22 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15555,22 +15555,22 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15592,17 +15592,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15624,17 +15624,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15661,12 +15661,12 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -15688,17 +15688,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15720,17 +15720,17 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15747,22 +15747,22 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15784,17 +15784,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15816,17 +15816,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15848,17 +15848,17 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15880,17 +15880,17 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15912,17 +15912,17 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15944,17 +15944,17 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道服务中心</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15971,22 +15971,22 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16008,17 +16008,17 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16040,17 +16040,17 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16072,17 +16072,17 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -16104,17 +16104,17 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16136,17 +16136,17 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16168,17 +16168,17 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16195,22 +16195,22 @@
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -16232,17 +16232,17 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16264,17 +16264,17 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16291,22 +16291,22 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16328,17 +16328,17 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16360,17 +16360,17 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16387,22 +16387,22 @@
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16424,17 +16424,17 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -16456,17 +16456,17 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16488,17 +16488,17 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16520,17 +16520,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16552,17 +16552,17 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16584,17 +16584,17 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16616,17 +16616,17 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16648,17 +16648,17 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -16675,22 +16675,22 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中信恒业</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中源恒业</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16707,22 +16707,22 @@
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16739,7 +16739,7 @@
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
@@ -16749,12 +16749,12 @@
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -16776,17 +16776,17 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16808,17 +16808,17 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16840,17 +16840,17 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -16872,17 +16872,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16904,17 +16904,17 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16936,17 +16936,17 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16968,17 +16968,17 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -17000,17 +17000,17 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17032,17 +17032,17 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -17064,17 +17064,17 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17096,17 +17096,17 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17128,17 +17128,17 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17160,17 +17160,17 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17192,17 +17192,17 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17224,17 +17224,17 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17256,17 +17256,17 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17283,22 +17283,22 @@
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17320,17 +17320,17 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17352,17 +17352,17 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17384,17 +17384,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17416,17 +17416,17 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17448,17 +17448,17 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17480,17 +17480,17 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17512,17 +17512,17 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17544,17 +17544,17 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -17571,22 +17571,22 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17603,22 +17603,22 @@
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17640,17 +17640,17 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17672,17 +17672,17 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17704,17 +17704,17 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17736,17 +17736,17 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17768,17 +17768,17 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17800,17 +17800,17 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17832,17 +17832,17 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17864,17 +17864,17 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17896,17 +17896,17 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17928,17 +17928,17 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17960,17 +17960,17 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -17992,17 +17992,17 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18029,12 +18029,12 @@
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18051,22 +18051,22 @@
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18083,22 +18083,22 @@
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>牡丹江中信恒业</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>牡丹江中源恒业</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18120,17 +18120,17 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -18147,22 +18147,22 @@
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18184,17 +18184,17 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -18216,17 +18216,17 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18248,17 +18248,17 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -18280,17 +18280,17 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -18312,17 +18312,17 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -18344,17 +18344,17 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -18376,17 +18376,17 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -18408,17 +18408,17 @@
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -18440,17 +18440,17 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -18472,17 +18472,17 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -18504,17 +18504,17 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -18536,17 +18536,17 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -18563,22 +18563,22 @@
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
@@ -18595,22 +18595,22 @@
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•威海青岛南路</t>
+          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
+          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
@@ -18620,29 +18620,29 @@
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 69%</t>
+          <t>地址相似度 60%</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
+          <t>鸿蒙智行尚界用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
+          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
@@ -18652,7 +18652,7 @@
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 60%</t>
+          <t>地址相似度 69%</t>
         </is>
       </c>
     </row>
@@ -18669,12 +18669,12 @@
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
+          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
+          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
@@ -18701,12 +18701,12 @@
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
@@ -18728,17 +18728,17 @@
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
@@ -18748,7 +18748,7 @@
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18792,17 +18792,17 @@
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
+          <t>小米汽车江西萍乡安源区萍乡天虹</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
+          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
@@ -18851,22 +18851,22 @@
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西萍乡安源区萍乡天虹</t>
+          <t>潍坊易豪4S中心</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
+          <t>潍坊鑫易豪4S中心</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
@@ -18876,7 +18876,7 @@
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
@@ -18888,17 +18888,17 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路授权服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
@@ -18908,7 +18908,7 @@
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 91%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18920,17 +18920,17 @@
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
+          <t>小米汽车兴义市桔康路授权服务中心</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
+          <t>小米汽车兴义市桔康路服务中心</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
@@ -18940,7 +18940,7 @@
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 91%</t>
         </is>
       </c>
     </row>
@@ -18952,17 +18952,17 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
@@ -18984,17 +18984,17 @@
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -19016,17 +19016,17 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
@@ -19043,22 +19043,22 @@
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>潍坊易豪4S中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>潍坊鑫易豪4S中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（46家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（63家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（186条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（46家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（63家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（186条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市江津区爱情海购物广场</t>
+          <t>小米汽车重庆市永川区永川万达</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>重庆市江津区爱情海购物广场L1层中庭</t>
+          <t>中国重庆市永川区星光大道789号永川万达</t>
         </is>
       </c>
     </row>
@@ -10353,7 +10353,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区永川万达</t>
+          <t>小米汽车重庆市江津区爱情海购物广场</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>中国重庆市永川区星光大道789号永川万达</t>
+          <t>重庆市江津区爱情海购物广场L1层中庭</t>
         </is>
       </c>
     </row>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>理想汽车潍坊青州汽车园零售展厅</t>
+          <t>理想汽车潍坊寿光授权钣喷中心（广宝店）</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>青州市玲珑山北路2359号</t>
+          <t>山东省潍坊市寿光市文家街道圣城西街666号</t>
         </is>
       </c>
     </row>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>理想汽车潍坊寿光授权钣喷中心（广宝店）</t>
+          <t>理想汽车潍坊青州汽车园零售展厅</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>山东省潍坊市寿光市文家街道圣城西街666号</t>
+          <t>青州市玲珑山北路2359号</t>
         </is>
       </c>
     </row>
@@ -10893,7 +10893,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南世纪大道万达广场</t>
+          <t>蔚来空间 | 济南西城龙湖天街广场</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
+          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
         </is>
       </c>
     </row>
@@ -10920,7 +10920,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南西城龙湖天街广场</t>
+          <t>蔚来空间 | 济南世纪大道万达广场</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
+          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
         </is>
       </c>
     </row>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京颐堤港</t>
+          <t>鸿蒙智行授权用户中心•北京王四营</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
+          <t>北京市朝阳区王四营339号</t>
         </is>
       </c>
     </row>
@@ -12210,7 +12210,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京王四营</t>
+          <t>华为智能生活馆•北京颐堤港</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营339号</t>
+          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（星河COCOCity）</t>
+          <t>华为授权体验店（南湖天地）</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
+          <t>浙江省嘉兴市南湖区南湖街道171号</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（西田城）</t>
+          <t>华为授权体验店（星河COCOCity）</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
+          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
         </is>
       </c>
     </row>
@@ -12804,7 +12804,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（南湖天地）</t>
+          <t>华为授权体验店（西田城）</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区南湖街道171号</t>
+          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
         </is>
       </c>
     </row>
@@ -13123,22 +13123,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
         </is>
       </c>
     </row>
@@ -13187,22 +13187,22 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13212,29 +13212,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
         </is>
       </c>
     </row>
@@ -13256,17 +13256,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13276,7 +13276,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
@@ -13288,17 +13288,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13308,29 +13308,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13340,29 +13340,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13372,29 +13372,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13404,29 +13404,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
+          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
+          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
         </is>
       </c>
     </row>
@@ -13448,17 +13448,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13468,29 +13468,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13500,29 +13500,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
+          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13532,29 +13532,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13564,14 +13564,14 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -13581,12 +13581,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13596,7 +13596,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
@@ -13635,22 +13635,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13660,29 +13660,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
+          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13692,7 +13692,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
+          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
         </is>
       </c>
     </row>
@@ -13704,17 +13704,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13724,29 +13724,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13756,29 +13756,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13788,29 +13788,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13820,29 +13820,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13852,29 +13852,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
         </is>
       </c>
     </row>
@@ -13896,17 +13896,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
@@ -13928,17 +13928,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13948,29 +13948,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13980,29 +13980,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14012,7 +14012,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
@@ -14051,22 +14051,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14076,29 +14076,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
+          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14108,29 +14108,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14140,7 +14140,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
+          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
         </is>
       </c>
     </row>
@@ -14152,17 +14152,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
@@ -14221,12 +14221,12 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14248,17 +14248,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14280,17 +14280,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14312,17 +14312,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14344,17 +14344,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14376,17 +14376,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14408,17 +14408,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14440,17 +14440,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14472,17 +14472,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14504,17 +14504,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14531,22 +14531,22 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14568,17 +14568,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14595,22 +14595,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14632,17 +14632,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14664,17 +14664,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14691,22 +14691,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14728,17 +14728,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14755,22 +14755,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14792,17 +14792,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14829,12 +14829,12 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14856,17 +14856,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14888,17 +14888,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14952,17 +14952,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14979,22 +14979,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15016,17 +15016,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15048,17 +15048,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15080,17 +15080,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15112,17 +15112,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15144,17 +15144,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15176,17 +15176,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15208,17 +15208,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15240,17 +15240,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15272,17 +15272,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15304,17 +15304,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15336,17 +15336,17 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15368,17 +15368,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15395,22 +15395,22 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15432,17 +15432,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -15459,7 +15459,7 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
@@ -15469,12 +15469,12 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15491,22 +15491,22 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>牡丹江中信恒业</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>牡丹江中源恒业</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15523,22 +15523,22 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15560,17 +15560,17 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15592,17 +15592,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15624,17 +15624,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15656,17 +15656,17 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -15688,17 +15688,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15720,17 +15720,17 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15747,22 +15747,22 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15784,17 +15784,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15816,17 +15816,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15848,17 +15848,17 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15880,17 +15880,17 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15912,17 +15912,17 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15944,17 +15944,17 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15976,17 +15976,17 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16008,17 +16008,17 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16040,17 +16040,17 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16072,17 +16072,17 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -16104,17 +16104,17 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16131,22 +16131,22 @@
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16168,17 +16168,17 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16200,17 +16200,17 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -16232,17 +16232,17 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16269,12 +16269,12 @@
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16291,22 +16291,22 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16328,17 +16328,17 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16360,17 +16360,17 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16392,17 +16392,17 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道服务中心</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16429,12 +16429,12 @@
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -16456,17 +16456,17 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16488,17 +16488,17 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16520,17 +16520,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16557,12 +16557,12 @@
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16584,17 +16584,17 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16616,17 +16616,17 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16648,17 +16648,17 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -16680,17 +16680,17 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16707,22 +16707,22 @@
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16739,22 +16739,22 @@
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -16776,17 +16776,17 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16808,17 +16808,17 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16835,22 +16835,22 @@
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -16872,17 +16872,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16904,17 +16904,17 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16931,22 +16931,22 @@
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16968,17 +16968,17 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -17000,17 +17000,17 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17032,17 +17032,17 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -17064,17 +17064,17 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17096,17 +17096,17 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17123,22 +17123,22 @@
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17160,17 +17160,17 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17192,17 +17192,17 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17224,17 +17224,17 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17251,22 +17251,22 @@
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17283,22 +17283,22 @@
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17320,17 +17320,17 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17357,12 +17357,12 @@
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17384,17 +17384,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17416,17 +17416,17 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17448,17 +17448,17 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17480,17 +17480,17 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17507,22 +17507,22 @@
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17544,17 +17544,17 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -17571,22 +17571,22 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17608,17 +17608,17 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17640,17 +17640,17 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17672,17 +17672,17 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17704,17 +17704,17 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17736,17 +17736,17 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17768,17 +17768,17 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17795,22 +17795,22 @@
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17832,17 +17832,17 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17864,17 +17864,17 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17896,17 +17896,17 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17928,17 +17928,17 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17955,22 +17955,22 @@
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -17992,17 +17992,17 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18024,17 +18024,17 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18056,17 +18056,17 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18083,22 +18083,22 @@
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中信恒业</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中源恒业</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18120,17 +18120,17 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -18147,22 +18147,22 @@
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18189,12 +18189,12 @@
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -18216,17 +18216,17 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18248,17 +18248,17 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -18280,17 +18280,17 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -18312,17 +18312,17 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -18344,17 +18344,17 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -18376,17 +18376,17 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -18440,17 +18440,17 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -18477,12 +18477,12 @@
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -18504,17 +18504,17 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -18536,17 +18536,17 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -18563,22 +18563,22 @@
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
@@ -18595,22 +18595,22 @@
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
+          <t>鸿蒙智行尚界用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
+          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
@@ -18620,29 +18620,29 @@
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 60%</t>
+          <t>地址相似度 69%</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•威海青岛南路</t>
+          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
+          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
@@ -18652,7 +18652,7 @@
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 69%</t>
+          <t>地址相似度 60%</t>
         </is>
       </c>
     </row>
@@ -18669,12 +18669,12 @@
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
@@ -18701,12 +18701,12 @@
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
+          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
+          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
@@ -18728,17 +18728,17 @@
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
@@ -18748,7 +18748,7 @@
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18760,17 +18760,17 @@
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路授权服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
@@ -18780,7 +18780,7 @@
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18792,17 +18792,17 @@
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西萍乡安源区萍乡天虹</t>
+          <t>小米汽车兴义市桔康路授权服务中心</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
+          <t>小米汽车兴义市桔康路服务中心</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
@@ -18812,7 +18812,7 @@
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 91%</t>
         </is>
       </c>
     </row>
@@ -18824,17 +18824,17 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
+          <t>小米汽车江西萍乡安源区萍乡天虹</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
+          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
@@ -18851,22 +18851,22 @@
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>潍坊易豪4S中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>潍坊鑫易豪4S中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
@@ -18876,29 +18876,29 @@
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
+          <t>潍坊易豪4S中心</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
+          <t>潍坊鑫易豪4S中心</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
@@ -18908,7 +18908,7 @@
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
@@ -18920,17 +18920,17 @@
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路授权服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
@@ -18940,7 +18940,7 @@
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 91%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18952,17 +18952,17 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>小米汽车天津西青区卫津南路授权服务中心</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>小米汽车天津西青区卫津南路服务中心</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
@@ -18972,7 +18972,7 @@
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18984,17 +18984,17 @@
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
@@ -19016,17 +19016,17 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
@@ -19036,7 +19036,7 @@
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -19048,17 +19048,17 @@
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（46家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（63家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（186条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（46家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（63家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（186条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区永川万达</t>
+          <t>小米汽车重庆市江津区爱情海购物广场</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>中国重庆市永川区星光大道789号永川万达</t>
+          <t>重庆市江津区爱情海购物广场L1层中庭</t>
         </is>
       </c>
     </row>
@@ -10353,7 +10353,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市江津区爱情海购物广场</t>
+          <t>小米汽车重庆市永川区永川万达</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>重庆市江津区爱情海购物广场L1层中庭</t>
+          <t>中国重庆市永川区星光大道789号永川万达</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春华润万象城零售中心</t>
+          <t>理想汽车长春中东新天地零售中心</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
+          <t>吉林省长春市南关区亚泰大街1138号</t>
         </is>
       </c>
     </row>
@@ -10569,7 +10569,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春中东新天地零售中心</t>
+          <t>理想汽车长春华润万象城零售中心</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区亚泰大街1138号</t>
+          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
         </is>
       </c>
     </row>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>理想汽车潍坊寿光授权钣喷中心（广宝店）</t>
+          <t>理想汽车潍坊青州汽车园零售展厅</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>山东省潍坊市寿光市文家街道圣城西街666号</t>
+          <t>青州市玲珑山北路2359号</t>
         </is>
       </c>
     </row>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>理想汽车潍坊青州汽车园零售展厅</t>
+          <t>理想汽车潍坊寿光授权钣喷中心（广宝店）</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>青州市玲珑山北路2359号</t>
+          <t>山东省潍坊市寿光市文家街道圣城西街666号</t>
         </is>
       </c>
     </row>
@@ -10893,7 +10893,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南西城龙湖天街广场</t>
+          <t>蔚来空间 | 济南世纪大道万达广场</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
+          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
         </is>
       </c>
     </row>
@@ -10920,7 +10920,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南世纪大道万达广场</t>
+          <t>蔚来空间 | 济南西城龙湖天街广场</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
+          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•成都惠王陵西路</t>
+          <t>鸿蒙智行智界用户中心•成都武侯大道</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市龙泉驿区惠王陵西路155号</t>
+          <t>四川省成都市武侯区武侯大道顺江段61号</t>
         </is>
       </c>
     </row>
@@ -11055,7 +11055,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•成都武侯大道</t>
+          <t>鸿蒙智行尚界用户中心•成都惠王陵西路</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市武侯区武侯大道顺江段61号</t>
+          <t>四川省成都市龙泉驿区惠王陵西路155号</t>
         </is>
       </c>
     </row>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>理想汽车江门江海零售中心</t>
+          <t>理想汽车江门江海服务中心（利生车城店）</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>江门市江海区银帆路2号5幢-2</t>
+          <t>广东省江门市江海区银帆路2号5幢(利生车城)</t>
         </is>
       </c>
     </row>
@@ -11805,7 +11805,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>理想汽车江门江海服务中心（利生车城店）</t>
+          <t>理想汽车江门江海零售中心</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>广东省江门市江海区银帆路2号5幢(利生车城)</t>
+          <t>江门市江海区银帆路2号5幢-2</t>
         </is>
       </c>
     </row>
@@ -12075,7 +12075,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-罗湖卫星展厅</t>
+          <t>深圳中升悦晟-福田电气化体验馆</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
+          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
         </is>
       </c>
     </row>
@@ -12102,7 +12102,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-福田电气化体验馆</t>
+          <t>深圳中升悦晟-罗湖卫星展厅</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
+          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
         </is>
       </c>
     </row>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京王四营</t>
+          <t>华为授权体验店（长楹龙湖）</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营339号</t>
+          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
         </is>
       </c>
     </row>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（长楹龙湖）</t>
+          <t>鸿蒙智行授权用户中心•北京王四营</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
+          <t>北京市朝阳区王四营339号</t>
         </is>
       </c>
     </row>
@@ -12480,7 +12480,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛乐客城</t>
+          <t>华为智能生活馆•青岛凯德Mall</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
+          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛凯德Mall</t>
+          <t>华为智能生活馆•青岛乐客城</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
+          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（星河COCOCity）</t>
+          <t>华为授权体验店（西田城）</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
+          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
         </is>
       </c>
     </row>
@@ -12804,7 +12804,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（西田城）</t>
+          <t>华为授权体验店（星河COCOCity）</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
+          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
         </is>
       </c>
     </row>
@@ -13160,17 +13160,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13180,29 +13180,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13212,29 +13212,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
+          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13244,29 +13244,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13276,29 +13276,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13308,29 +13308,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13340,29 +13340,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
+          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13372,7 +13372,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
@@ -13384,17 +13384,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13404,29 +13404,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13436,29 +13436,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13468,29 +13468,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13500,29 +13500,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
+          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13532,29 +13532,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13564,7 +13564,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
+          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
         </is>
       </c>
     </row>
@@ -13576,17 +13576,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13596,29 +13596,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>广东省珠海市香洲区前山工业区华威路103号A-23号 → 广东省珠海市香洲区前山工业区华威路103号二手车车库103-A-23号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13628,29 +13628,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13660,29 +13660,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
+          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13692,29 +13692,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13724,29 +13724,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
+          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
@@ -13768,17 +13768,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13788,29 +13788,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13820,29 +13820,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
+          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13852,7 +13852,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
         </is>
       </c>
     </row>
@@ -13896,17 +13896,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
         </is>
       </c>
     </row>
@@ -13928,17 +13928,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13948,29 +13948,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13980,29 +13980,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14012,7 +14012,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
         </is>
       </c>
     </row>
@@ -14024,17 +14024,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•珠海香洲上冲汽车城</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14044,29 +14044,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>广东省珠海市香洲区前山工业区华威路103号A-23号 → 广东省珠海市香洲区前山工业区华威路103号二手车车库103-A-23号</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14076,29 +14076,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14108,29 +14108,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14140,29 +14140,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
         </is>
       </c>
     </row>
@@ -14216,17 +14216,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14243,22 +14243,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14280,17 +14280,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14312,17 +14312,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14349,12 +14349,12 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14376,17 +14376,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14408,17 +14408,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14440,17 +14440,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14472,17 +14472,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14509,12 +14509,12 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14531,22 +14531,22 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14568,17 +14568,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14595,22 +14595,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14632,17 +14632,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14664,17 +14664,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14696,17 +14696,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14728,17 +14728,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14760,17 +14760,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14792,17 +14792,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14824,17 +14824,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14856,17 +14856,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14888,17 +14888,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14915,7 +14915,7 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14952,17 +14952,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14984,17 +14984,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15021,12 +15021,12 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15048,17 +15048,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15080,17 +15080,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15112,17 +15112,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15144,17 +15144,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15176,17 +15176,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15208,17 +15208,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15240,17 +15240,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15272,17 +15272,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15304,17 +15304,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15331,7 +15331,7 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15368,17 +15368,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15395,22 +15395,22 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15432,17 +15432,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -15459,22 +15459,22 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15491,22 +15491,22 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中信恒业</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中源恒业</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15533,12 +15533,12 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15560,17 +15560,17 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15592,17 +15592,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15624,17 +15624,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15656,17 +15656,17 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -15688,17 +15688,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15715,22 +15715,22 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15752,17 +15752,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15784,17 +15784,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15816,17 +15816,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15848,17 +15848,17 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15880,17 +15880,17 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15912,17 +15912,17 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15944,17 +15944,17 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15976,17 +15976,17 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16008,17 +16008,17 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16040,17 +16040,17 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16072,17 +16072,17 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -16104,17 +16104,17 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16131,22 +16131,22 @@
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16168,17 +16168,17 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16200,17 +16200,17 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -16227,22 +16227,22 @@
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>牡丹江中信恒业</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>牡丹江中源恒业</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16264,17 +16264,17 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16296,17 +16296,17 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16328,17 +16328,17 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16360,17 +16360,17 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16392,17 +16392,17 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16424,17 +16424,17 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -16456,17 +16456,17 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16488,17 +16488,17 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16520,17 +16520,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16557,12 +16557,12 @@
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16584,17 +16584,17 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16616,17 +16616,17 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16648,17 +16648,17 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -16680,17 +16680,17 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16712,17 +16712,17 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16744,17 +16744,17 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -16776,17 +16776,17 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16808,17 +16808,17 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16835,22 +16835,22 @@
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -16872,17 +16872,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16904,17 +16904,17 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16931,22 +16931,22 @@
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16968,17 +16968,17 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -17000,17 +17000,17 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17064,17 +17064,17 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17096,17 +17096,17 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17123,22 +17123,22 @@
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17160,17 +17160,17 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17192,17 +17192,17 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17224,17 +17224,17 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17256,17 +17256,17 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17288,17 +17288,17 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17320,17 +17320,17 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17347,22 +17347,22 @@
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17384,17 +17384,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17416,17 +17416,17 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17448,17 +17448,17 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17480,17 +17480,17 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17507,7 +17507,7 @@
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
@@ -17517,12 +17517,12 @@
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17544,17 +17544,17 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -17576,17 +17576,17 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17603,22 +17603,22 @@
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17640,17 +17640,17 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17672,17 +17672,17 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17704,17 +17704,17 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道服务中心</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17736,17 +17736,17 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17773,12 +17773,12 @@
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17795,22 +17795,22 @@
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17832,17 +17832,17 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17864,17 +17864,17 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17896,17 +17896,17 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17928,17 +17928,17 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17960,17 +17960,17 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -17992,17 +17992,17 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18024,17 +18024,17 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18051,22 +18051,22 @@
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18088,17 +18088,17 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18120,17 +18120,17 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -18152,17 +18152,17 @@
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18179,22 +18179,22 @@
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -18216,17 +18216,17 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18248,17 +18248,17 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -18280,17 +18280,17 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -18312,17 +18312,17 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -18344,17 +18344,17 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -18376,17 +18376,17 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -18408,17 +18408,17 @@
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -18440,17 +18440,17 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -18472,17 +18472,17 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -18504,17 +18504,17 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -18536,17 +18536,17 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -18573,12 +18573,12 @@
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
@@ -18595,22 +18595,22 @@
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•威海青岛南路</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
@@ -18620,29 +18620,29 @@
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 69%</t>
+          <t>地址相似度 88%</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
+          <t>鸿蒙智行尚界用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
+          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
@@ -18652,7 +18652,7 @@
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 60%</t>
+          <t>地址相似度 69%</t>
         </is>
       </c>
     </row>
@@ -18669,12 +18669,12 @@
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
+          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
+          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
@@ -18691,22 +18691,22 @@
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
+          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
+          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 88%</t>
+          <t>地址相似度 60%</t>
         </is>
       </c>
     </row>
@@ -18728,17 +18728,17 @@
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
+          <t>小米汽车江西萍乡安源区萍乡天虹</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
+          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
@@ -18748,7 +18748,7 @@
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18760,17 +18760,17 @@
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
@@ -18780,7 +18780,7 @@
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18792,17 +18792,17 @@
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路授权服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
@@ -18812,7 +18812,7 @@
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 91%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18824,17 +18824,17 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西萍乡安源区萍乡天虹</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18856,17 +18856,17 @@
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
@@ -18883,22 +18883,22 @@
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>潍坊易豪4S中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>潍坊鑫易豪4S中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
@@ -18908,7 +18908,7 @@
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18920,17 +18920,17 @@
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
+          <t>小米汽车天津西青区卫津南路授权服务中心</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
+          <t>小米汽车天津西青区卫津南路服务中心</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
@@ -18940,7 +18940,7 @@
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18952,17 +18952,17 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路授权服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
@@ -18984,17 +18984,17 @@
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
@@ -19004,29 +19004,29 @@
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
+          <t>潍坊易豪4S中心</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
+          <t>潍坊鑫易豪4S中心</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
@@ -19036,7 +19036,7 @@
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
@@ -19048,17 +19048,17 @@
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>小米汽车兴义市桔康路授权服务中心</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>小米汽车兴义市桔康路服务中心</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 91%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（46家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（63家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（186条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（46家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（63家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（186条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10083,7 +10083,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区西四环双林东路服务中心</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>双林东路8号万开基地二期B座</t>
+          <t>北京市大兴区大兴龙湖天街一层中庭</t>
         </is>
       </c>
     </row>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京丰台区西四环双林东路服务中心</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>北京市大兴区大兴龙湖天街一层中庭</t>
+          <t>双林东路8号万开基地二期B座</t>
         </is>
       </c>
     </row>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>理想汽车潍坊青州汽车园零售展厅</t>
+          <t>理想汽车潍坊寿光授权钣喷中心（广宝店）</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>青州市玲珑山北路2359号</t>
+          <t>山东省潍坊市寿光市文家街道圣城西街666号</t>
         </is>
       </c>
     </row>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>理想汽车潍坊寿光授权钣喷中心（广宝店）</t>
+          <t>理想汽车潍坊青州汽车园零售展厅</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>山东省潍坊市寿光市文家街道圣城西街666号</t>
+          <t>青州市玲珑山北路2359号</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
+          <t>AITO授权用户中心•宁波下应</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•宁波下应</t>
+          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>理想汽车衢州吾悦广场零售中心</t>
+          <t>理想汽车衢州衢江服务中心（振兴东路店）</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区白云中大道路99号吾悦广场1019-1商铺理想汽车</t>
+          <t>衢州市衢江区振兴东路599号</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江服务中心（振兴东路店）</t>
+          <t>理想汽车衢州吾悦广场零售中心</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>衢州市衢江区振兴东路599号</t>
+          <t>浙江省衢州市柯城区白云中大道路99号吾悦广场1019-1商铺理想汽车</t>
         </is>
       </c>
     </row>
@@ -12075,7 +12075,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-福田电气化体验馆</t>
+          <t>深圳中升悦晟-罗湖卫星展厅</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
+          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
         </is>
       </c>
     </row>
@@ -12102,7 +12102,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-罗湖卫星展厅</t>
+          <t>深圳中升悦晟-福田电气化体验馆</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
+          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
         </is>
       </c>
     </row>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（长楹龙湖）</t>
+          <t>鸿蒙智行授权用户中心•北京王四营</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
+          <t>北京市朝阳区王四营339号</t>
         </is>
       </c>
     </row>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京王四营</t>
+          <t>华为授权体验店（长楹龙湖）</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营339号</t>
+          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
         </is>
       </c>
     </row>
@@ -12480,7 +12480,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛凯德Mall</t>
+          <t>华为智能生活馆•青岛乐客城</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
+          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛乐客城</t>
+          <t>华为智能生活馆•青岛凯德Mall</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
+          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（南湖天地）</t>
+          <t>华为授权体验店（星河COCOCity）</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区南湖街道171号</t>
+          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
         </is>
       </c>
     </row>
@@ -12804,7 +12804,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（星河COCOCity）</t>
+          <t>华为授权体验店（南湖天地）</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
+          <t>浙江省嘉兴市南湖区南湖街道171号</t>
         </is>
       </c>
     </row>
@@ -13123,22 +13123,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13148,29 +13148,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
@@ -13192,17 +13192,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13212,29 +13212,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13244,29 +13244,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13276,29 +13276,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C7" s="5"